--- a/static/template-grille-audit-simplifie.xlsx
+++ b/static/template-grille-audit-simplifie.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\sip\simplA11yMonit\static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\sip\simplified_audits\simplA11yMonit\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380A1D0B-87A3-4359-BD3F-BD8389C1D78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B230F03E-9CE4-4A62-B4C2-29EF5B907F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2490" yWindow="1440" windowWidth="23445" windowHeight="12600" tabRatio="861" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41595" yWindow="2805" windowWidth="28800" windowHeight="15345" tabRatio="861" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Échantillon" sheetId="2" r:id="rId1"/>
@@ -1206,11 +1206,13 @@
       <sz val="12"/>
       <color theme="0"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1948,15 +1950,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="25" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="26" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="27" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -1969,25 +1962,34 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="2" xfId="12" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="25" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="26" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="27" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="19" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="23" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="21" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="19" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="23" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="21" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="12" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -5371,15 +5373,15 @@
       <c r="F41" s="25"/>
       <c r="G41" s="25"/>
       <c r="H41" s="26">
-        <f>SUM(H34:H40)</f>
+        <f>SUM(H33:H40)</f>
         <v>0</v>
       </c>
       <c r="I41" s="26">
-        <f t="shared" ref="I41:J41" si="32">SUM(I34:I40)</f>
+        <f>SUM(I33:I40)</f>
         <v>0</v>
       </c>
       <c r="J41" s="26">
-        <f t="shared" si="32"/>
+        <f>SUM(J33:J40)</f>
         <v>0</v>
       </c>
       <c r="K41" s="26">
@@ -5612,23 +5614,23 @@
         <v>NT</v>
       </c>
       <c r="H45" s="23">
-        <f t="shared" ref="H45:H49" si="33">COUNTIF(E45:G45,"C")</f>
+        <f t="shared" ref="H45:H49" si="32">COUNTIF(E45:G45,"C")</f>
         <v>0</v>
       </c>
       <c r="I45" s="23">
-        <f t="shared" ref="I45:I49" si="34">COUNTIF(E45:G45,"NC")</f>
+        <f t="shared" ref="I45:I49" si="33">COUNTIF(E45:G45,"NC")</f>
         <v>0</v>
       </c>
       <c r="J45" s="23">
-        <f t="shared" ref="J45:J49" si="35">COUNTIF(E45:G45,"NA")</f>
+        <f t="shared" ref="J45:J49" si="34">COUNTIF(E45:G45,"NA")</f>
         <v>0</v>
       </c>
       <c r="K45" s="23">
-        <f t="shared" ref="K45:K49" si="36">COUNTIF(E45:G45,"NT")</f>
+        <f t="shared" ref="K45:K49" si="35">COUNTIF(E45:G45,"NT")</f>
         <v>3</v>
       </c>
       <c r="L45" s="15" t="str">
-        <f t="shared" ref="L45:L49" si="37">IF(I45&gt;0,"NC",IF(H45&gt;0,"C",IF(K45&gt;0,"NT","NA")))</f>
+        <f t="shared" ref="L45:L49" si="36">IF(I45&gt;0,"NC",IF(H45&gt;0,"C",IF(K45&gt;0,"NT","NA")))</f>
         <v>NT</v>
       </c>
       <c r="M45" s="15">
@@ -5655,7 +5657,7 @@
         <v>N</v>
       </c>
       <c r="S45" s="23">
-        <f t="shared" ref="S45:S49" si="38">COUNTIF(P45:R45,"D")</f>
+        <f t="shared" ref="S45:S49" si="37">COUNTIF(P45:R45,"D")</f>
         <v>0</v>
       </c>
     </row>
@@ -5687,23 +5689,23 @@
         <v>NT</v>
       </c>
       <c r="H46" s="23">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="23">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="I46" s="23">
+      <c r="J46" s="23">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="J46" s="23">
+      <c r="K46" s="23">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="K46" s="23">
+        <v>3</v>
+      </c>
+      <c r="L46" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>3</v>
-      </c>
-      <c r="L46" s="15" t="str">
-        <f t="shared" si="37"/>
         <v>NT</v>
       </c>
       <c r="M46" s="15">
@@ -5730,7 +5732,7 @@
         <v>N</v>
       </c>
       <c r="S46" s="23">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
@@ -5762,23 +5764,23 @@
         <v>NT</v>
       </c>
       <c r="H47" s="23">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="I47" s="23">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="I47" s="23">
+      <c r="J47" s="23">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="J47" s="23">
+      <c r="K47" s="23">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="K47" s="23">
+        <v>3</v>
+      </c>
+      <c r="L47" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>3</v>
-      </c>
-      <c r="L47" s="15" t="str">
-        <f t="shared" si="37"/>
         <v>NT</v>
       </c>
       <c r="M47" s="15">
@@ -5805,7 +5807,7 @@
         <v>N</v>
       </c>
       <c r="S47" s="23">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
@@ -5837,23 +5839,23 @@
         <v>NT</v>
       </c>
       <c r="H48" s="23">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="23">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="I48" s="23">
+      <c r="J48" s="23">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="J48" s="23">
+      <c r="K48" s="23">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="K48" s="23">
+        <v>3</v>
+      </c>
+      <c r="L48" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>3</v>
-      </c>
-      <c r="L48" s="15" t="str">
-        <f t="shared" si="37"/>
         <v>NT</v>
       </c>
       <c r="M48" s="15">
@@ -5880,7 +5882,7 @@
         <v>N</v>
       </c>
       <c r="S48" s="23">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
@@ -5912,23 +5914,23 @@
         <v>NT</v>
       </c>
       <c r="H49" s="23">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="23">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="I49" s="23">
+      <c r="J49" s="23">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="J49" s="23">
+      <c r="K49" s="23">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="K49" s="23">
+        <v>3</v>
+      </c>
+      <c r="L49" s="15" t="str">
         <f t="shared" si="36"/>
-        <v>3</v>
-      </c>
-      <c r="L49" s="15" t="str">
-        <f t="shared" si="37"/>
         <v>NT</v>
       </c>
       <c r="M49" s="15">
@@ -5955,7 +5957,7 @@
         <v>N</v>
       </c>
       <c r="S49" s="23">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
@@ -6023,23 +6025,23 @@
         <v>NT</v>
       </c>
       <c r="H51" s="23">
-        <f t="shared" ref="H51:H57" si="39">COUNTIF(E51:G51,"C")</f>
+        <f t="shared" ref="H51:H57" si="38">COUNTIF(E51:G51,"C")</f>
         <v>0</v>
       </c>
       <c r="I51" s="23">
-        <f t="shared" ref="I51:I57" si="40">COUNTIF(E51:G51,"NC")</f>
+        <f t="shared" ref="I51:I57" si="39">COUNTIF(E51:G51,"NC")</f>
         <v>0</v>
       </c>
       <c r="J51" s="23">
-        <f t="shared" ref="J51:J57" si="41">COUNTIF(E51:G51,"NA")</f>
+        <f t="shared" ref="J51:J57" si="40">COUNTIF(E51:G51,"NA")</f>
         <v>0</v>
       </c>
       <c r="K51" s="23">
-        <f t="shared" ref="K51:K57" si="42">COUNTIF(E51:G51,"NT")</f>
+        <f t="shared" ref="K51:K57" si="41">COUNTIF(E51:G51,"NT")</f>
         <v>3</v>
       </c>
       <c r="L51" s="15" t="str">
-        <f t="shared" ref="L51:L57" si="43">IF(I51&gt;0,"NC",IF(H51&gt;0,"C",IF(K51&gt;0,"NT","NA")))</f>
+        <f t="shared" ref="L51:L57" si="42">IF(I51&gt;0,"NC",IF(H51&gt;0,"C",IF(K51&gt;0,"NT","NA")))</f>
         <v>NT</v>
       </c>
       <c r="M51" s="15">
@@ -6066,7 +6068,7 @@
         <v>N</v>
       </c>
       <c r="S51" s="23">
-        <f t="shared" ref="S51:S57" si="44">COUNTIF(P51:R51,"D")</f>
+        <f t="shared" ref="S51:S57" si="43">COUNTIF(P51:R51,"D")</f>
         <v>0</v>
       </c>
     </row>
@@ -6098,23 +6100,23 @@
         <v>NT</v>
       </c>
       <c r="H52" s="23">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="I52" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="I52" s="23">
+      <c r="J52" s="23">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="J52" s="23">
+      <c r="K52" s="23">
         <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="K52" s="23">
+        <v>3</v>
+      </c>
+      <c r="L52" s="15" t="str">
         <f t="shared" si="42"/>
-        <v>3</v>
-      </c>
-      <c r="L52" s="15" t="str">
-        <f t="shared" si="43"/>
         <v>NT</v>
       </c>
       <c r="M52" s="15">
@@ -6141,7 +6143,7 @@
         <v>N</v>
       </c>
       <c r="S52" s="23">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
     </row>
@@ -6173,23 +6175,23 @@
         <v>NT</v>
       </c>
       <c r="H53" s="23">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="I53" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="I53" s="23">
+      <c r="J53" s="23">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="J53" s="23">
+      <c r="K53" s="23">
         <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="K53" s="23">
+        <v>3</v>
+      </c>
+      <c r="L53" s="15" t="str">
         <f t="shared" si="42"/>
-        <v>3</v>
-      </c>
-      <c r="L53" s="15" t="str">
-        <f t="shared" si="43"/>
         <v>NT</v>
       </c>
       <c r="M53" s="15">
@@ -6216,7 +6218,7 @@
         <v>N</v>
       </c>
       <c r="S53" s="23">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
     </row>
@@ -6248,23 +6250,23 @@
         <v>NT</v>
       </c>
       <c r="H54" s="23">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="I54" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="I54" s="23">
+      <c r="J54" s="23">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="J54" s="23">
+      <c r="K54" s="23">
         <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="K54" s="23">
+        <v>3</v>
+      </c>
+      <c r="L54" s="15" t="str">
         <f t="shared" si="42"/>
-        <v>3</v>
-      </c>
-      <c r="L54" s="15" t="str">
-        <f t="shared" si="43"/>
         <v>NT</v>
       </c>
       <c r="M54" s="15">
@@ -6291,7 +6293,7 @@
         <v>N</v>
       </c>
       <c r="S54" s="23">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
     </row>
@@ -6323,23 +6325,23 @@
         <v>NT</v>
       </c>
       <c r="H55" s="23">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="I55" s="23">
+      <c r="J55" s="23">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="J55" s="23">
+      <c r="K55" s="23">
         <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="K55" s="23">
+        <v>3</v>
+      </c>
+      <c r="L55" s="15" t="str">
         <f t="shared" si="42"/>
-        <v>3</v>
-      </c>
-      <c r="L55" s="15" t="str">
-        <f t="shared" si="43"/>
         <v>NT</v>
       </c>
       <c r="M55" s="15">
@@ -6366,7 +6368,7 @@
         <v>N</v>
       </c>
       <c r="S55" s="23">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
     </row>
@@ -6398,23 +6400,23 @@
         <v>NT</v>
       </c>
       <c r="H56" s="23">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="I56" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="I56" s="23">
+      <c r="J56" s="23">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="J56" s="23">
+      <c r="K56" s="23">
         <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="K56" s="23">
+        <v>3</v>
+      </c>
+      <c r="L56" s="15" t="str">
         <f t="shared" si="42"/>
-        <v>3</v>
-      </c>
-      <c r="L56" s="15" t="str">
-        <f t="shared" si="43"/>
         <v>NT</v>
       </c>
       <c r="M56" s="15">
@@ -6441,7 +6443,7 @@
         <v>N</v>
       </c>
       <c r="S56" s="23">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
     </row>
@@ -6473,23 +6475,23 @@
         <v>NT</v>
       </c>
       <c r="H57" s="23">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="I57" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="I57" s="23">
+      <c r="J57" s="23">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="J57" s="23">
+      <c r="K57" s="23">
         <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="K57" s="23">
+        <v>3</v>
+      </c>
+      <c r="L57" s="15" t="str">
         <f t="shared" si="42"/>
-        <v>3</v>
-      </c>
-      <c r="L57" s="15" t="str">
-        <f t="shared" si="43"/>
         <v>NT</v>
       </c>
       <c r="M57" s="15">
@@ -6516,7 +6518,7 @@
         <v>N</v>
       </c>
       <c r="S57" s="23">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
     </row>
@@ -6584,23 +6586,23 @@
         <v>NT</v>
       </c>
       <c r="H59" s="23">
-        <f t="shared" ref="H59:H63" si="45">COUNTIF(E59:G59,"C")</f>
+        <f t="shared" ref="H59:H63" si="44">COUNTIF(E59:G59,"C")</f>
         <v>0</v>
       </c>
       <c r="I59" s="23">
-        <f t="shared" ref="I59:I63" si="46">COUNTIF(E59:G59,"NC")</f>
+        <f t="shared" ref="I59:I63" si="45">COUNTIF(E59:G59,"NC")</f>
         <v>0</v>
       </c>
       <c r="J59" s="23">
-        <f t="shared" ref="J59:J63" si="47">COUNTIF(E59:G59,"NA")</f>
+        <f t="shared" ref="J59:J63" si="46">COUNTIF(E59:G59,"NA")</f>
         <v>0</v>
       </c>
       <c r="K59" s="23">
-        <f t="shared" ref="K59:K63" si="48">COUNTIF(E59:G59,"NT")</f>
+        <f t="shared" ref="K59:K63" si="47">COUNTIF(E59:G59,"NT")</f>
         <v>3</v>
       </c>
       <c r="L59" s="15" t="str">
-        <f t="shared" ref="L59:L63" si="49">IF(I59&gt;0,"NC",IF(H59&gt;0,"C",IF(K59&gt;0,"NT","NA")))</f>
+        <f t="shared" ref="L59:L63" si="48">IF(I59&gt;0,"NC",IF(H59&gt;0,"C",IF(K59&gt;0,"NT","NA")))</f>
         <v>NT</v>
       </c>
       <c r="M59" s="15">
@@ -6627,7 +6629,7 @@
         <v>N</v>
       </c>
       <c r="S59" s="23">
-        <f t="shared" ref="S59:S63" si="50">COUNTIF(P59:R59,"D")</f>
+        <f t="shared" ref="S59:S63" si="49">COUNTIF(P59:R59,"D")</f>
         <v>0</v>
       </c>
     </row>
@@ -6659,23 +6661,23 @@
         <v>NT</v>
       </c>
       <c r="H60" s="23">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="I60" s="23">
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="I60" s="23">
+      <c r="J60" s="23">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="J60" s="23">
+      <c r="K60" s="23">
         <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="K60" s="23">
+        <v>3</v>
+      </c>
+      <c r="L60" s="15" t="str">
         <f t="shared" si="48"/>
-        <v>3</v>
-      </c>
-      <c r="L60" s="15" t="str">
-        <f t="shared" si="49"/>
         <v>NT</v>
       </c>
       <c r="M60" s="15">
@@ -6702,7 +6704,7 @@
         <v>N</v>
       </c>
       <c r="S60" s="23">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
     </row>
@@ -6734,23 +6736,23 @@
         <v>NT</v>
       </c>
       <c r="H61" s="23">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="I61" s="23">
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="I61" s="23">
+      <c r="J61" s="23">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="J61" s="23">
+      <c r="K61" s="23">
         <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="K61" s="23">
+        <v>3</v>
+      </c>
+      <c r="L61" s="15" t="str">
         <f t="shared" si="48"/>
-        <v>3</v>
-      </c>
-      <c r="L61" s="15" t="str">
-        <f t="shared" si="49"/>
         <v>NT</v>
       </c>
       <c r="M61" s="15">
@@ -6777,7 +6779,7 @@
         <v>N</v>
       </c>
       <c r="S61" s="23">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
     </row>
@@ -6809,23 +6811,23 @@
         <v>NT</v>
       </c>
       <c r="H62" s="23">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="I62" s="23">
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="I62" s="23">
+      <c r="J62" s="23">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="J62" s="23">
+      <c r="K62" s="23">
         <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="K62" s="23">
+        <v>3</v>
+      </c>
+      <c r="L62" s="15" t="str">
         <f t="shared" si="48"/>
-        <v>3</v>
-      </c>
-      <c r="L62" s="15" t="str">
-        <f t="shared" si="49"/>
         <v>NT</v>
       </c>
       <c r="M62" s="15">
@@ -6852,7 +6854,7 @@
         <v>N</v>
       </c>
       <c r="S62" s="23">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
     </row>
@@ -6884,23 +6886,23 @@
         <v>NT</v>
       </c>
       <c r="H63" s="23">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="I63" s="23">
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="I63" s="23">
+      <c r="J63" s="23">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="J63" s="23">
+      <c r="K63" s="23">
         <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="K63" s="23">
+        <v>3</v>
+      </c>
+      <c r="L63" s="15" t="str">
         <f t="shared" si="48"/>
-        <v>3</v>
-      </c>
-      <c r="L63" s="15" t="str">
-        <f t="shared" si="49"/>
         <v>NT</v>
       </c>
       <c r="M63" s="15">
@@ -6927,7 +6929,7 @@
         <v>N</v>
       </c>
       <c r="S63" s="23">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
     </row>
@@ -6995,23 +6997,23 @@
         <v>NT</v>
       </c>
       <c r="H65" s="23">
-        <f t="shared" ref="H65:H67" si="51">COUNTIF(E65:G65,"C")</f>
+        <f t="shared" ref="H65:H67" si="50">COUNTIF(E65:G65,"C")</f>
         <v>0</v>
       </c>
       <c r="I65" s="23">
-        <f t="shared" ref="I65:I67" si="52">COUNTIF(E65:G65,"NC")</f>
+        <f t="shared" ref="I65:I67" si="51">COUNTIF(E65:G65,"NC")</f>
         <v>0</v>
       </c>
       <c r="J65" s="23">
-        <f t="shared" ref="J65:J67" si="53">COUNTIF(E65:G65,"NA")</f>
+        <f t="shared" ref="J65:J67" si="52">COUNTIF(E65:G65,"NA")</f>
         <v>0</v>
       </c>
       <c r="K65" s="23">
-        <f t="shared" ref="K65:K67" si="54">COUNTIF(E65:G65,"NT")</f>
+        <f t="shared" ref="K65:K67" si="53">COUNTIF(E65:G65,"NT")</f>
         <v>3</v>
       </c>
       <c r="L65" s="15" t="str">
-        <f t="shared" ref="L65:L67" si="55">IF(I65&gt;0,"NC",IF(H65&gt;0,"C",IF(K65&gt;0,"NT","NA")))</f>
+        <f t="shared" ref="L65:L67" si="54">IF(I65&gt;0,"NC",IF(H65&gt;0,"C",IF(K65&gt;0,"NT","NA")))</f>
         <v>NT</v>
       </c>
       <c r="M65" s="15">
@@ -7038,7 +7040,7 @@
         <v>N</v>
       </c>
       <c r="S65" s="23">
-        <f t="shared" ref="S65:S67" si="56">COUNTIF(P65:R65,"D")</f>
+        <f t="shared" ref="S65:S67" si="55">COUNTIF(P65:R65,"D")</f>
         <v>0</v>
       </c>
     </row>
@@ -7070,23 +7072,23 @@
         <v>NT</v>
       </c>
       <c r="H66" s="23">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="I66" s="23">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="I66" s="23">
+      <c r="J66" s="23">
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="J66" s="23">
+      <c r="K66" s="23">
         <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="K66" s="23">
+        <v>3</v>
+      </c>
+      <c r="L66" s="15" t="str">
         <f t="shared" si="54"/>
-        <v>3</v>
-      </c>
-      <c r="L66" s="15" t="str">
-        <f t="shared" si="55"/>
         <v>NT</v>
       </c>
       <c r="M66" s="15">
@@ -7113,7 +7115,7 @@
         <v>N</v>
       </c>
       <c r="S66" s="23">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
     </row>
@@ -7145,23 +7147,23 @@
         <v>NT</v>
       </c>
       <c r="H67" s="23">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="I67" s="23">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="I67" s="23">
+      <c r="J67" s="23">
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="J67" s="23">
+      <c r="K67" s="23">
         <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="K67" s="23">
+        <v>3</v>
+      </c>
+      <c r="L67" s="15" t="str">
         <f t="shared" si="54"/>
-        <v>3</v>
-      </c>
-      <c r="L67" s="15" t="str">
-        <f t="shared" si="55"/>
         <v>NT</v>
       </c>
       <c r="M67" s="15">
@@ -7188,7 +7190,7 @@
         <v>N</v>
       </c>
       <c r="S67" s="23">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
     </row>
@@ -7372,11 +7374,11 @@
         <v>NA</v>
       </c>
       <c r="F72" s="52" t="str">
-        <f t="shared" ref="F72:G72" si="57">IF(AND(F69=0,F70=0),"NA",F69/(F69+F70))</f>
+        <f t="shared" ref="F72:G72" si="56">IF(AND(F69=0,F70=0),"NA",F69/(F69+F70))</f>
         <v>NA</v>
       </c>
       <c r="G72" s="52" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>NA</v>
       </c>
       <c r="H72" s="28" t="e">
@@ -7413,11 +7415,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="F74" s="50" t="e">
-        <f t="shared" ref="F74:G74" si="58">F72*100</f>
+        <f t="shared" ref="F74:G74" si="57">F72*100</f>
         <v>#VALUE!</v>
       </c>
       <c r="G74" s="50" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7983,12 +7985,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="97" t="str">
+      <c r="A1" s="101" t="str">
         <f>Échantillon!A1</f>
         <v>AUDIT SIMPLIFIÉ – GRILLE D'ÉVALUATION</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="99"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
     </row>
     <row r="2" spans="1:4" ht="70.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="29" t="s">
@@ -8002,7 +8004,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="97" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="57" t="s">
@@ -8014,7 +8016,7 @@
       <c r="D3" s="6"/>
     </row>
     <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="100"/>
+      <c r="A4" s="97"/>
       <c r="B4" s="57" t="s">
         <v>13</v>
       </c>
@@ -8024,7 +8026,7 @@
       <c r="D4" s="6"/>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="100"/>
+      <c r="A5" s="97"/>
       <c r="B5" s="57" t="s">
         <v>14</v>
       </c>
@@ -8034,7 +8036,7 @@
       <c r="D5" s="6"/>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="100"/>
+      <c r="A6" s="97"/>
       <c r="B6" s="57" t="s">
         <v>16</v>
       </c>
@@ -8044,7 +8046,7 @@
       <c r="D6" s="6"/>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A7" s="100"/>
+      <c r="A7" s="97"/>
       <c r="B7" s="57" t="s">
         <v>17</v>
       </c>
@@ -8054,7 +8056,7 @@
       <c r="D7" s="6"/>
     </row>
     <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="100"/>
+      <c r="A8" s="97"/>
       <c r="B8" s="57" t="s">
         <v>18</v>
       </c>
@@ -8064,7 +8066,7 @@
       <c r="D8" s="6"/>
     </row>
     <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A9" s="100"/>
+      <c r="A9" s="97"/>
       <c r="B9" s="57" t="s">
         <v>19</v>
       </c>
@@ -8086,7 +8088,7 @@
       <c r="D10" s="6"/>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A11" s="100" t="s">
+      <c r="A11" s="97" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="57" t="s">
@@ -8098,7 +8100,7 @@
       <c r="D11" s="6"/>
     </row>
     <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A12" s="100"/>
+      <c r="A12" s="97"/>
       <c r="B12" s="57" t="s">
         <v>23</v>
       </c>
@@ -8108,7 +8110,7 @@
       <c r="D12" s="6"/>
     </row>
     <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A13" s="100" t="s">
+      <c r="A13" s="97" t="s">
         <v>24</v>
       </c>
       <c r="B13" s="57" t="s">
@@ -8120,7 +8122,7 @@
       <c r="D13" s="6"/>
     </row>
     <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A14" s="100"/>
+      <c r="A14" s="97"/>
       <c r="B14" s="57" t="s">
         <v>26</v>
       </c>
@@ -8130,7 +8132,7 @@
       <c r="D14" s="6"/>
     </row>
     <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="100"/>
+      <c r="A15" s="97"/>
       <c r="B15" s="57" t="s">
         <v>27</v>
       </c>
@@ -8140,7 +8142,7 @@
       <c r="D15" s="6"/>
     </row>
     <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A16" s="100"/>
+      <c r="A16" s="97"/>
       <c r="B16" s="57" t="s">
         <v>28</v>
       </c>
@@ -8150,7 +8152,7 @@
       <c r="D16" s="6"/>
     </row>
     <row r="17" spans="1:64" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17" s="100"/>
+      <c r="A17" s="97"/>
       <c r="B17" s="57" t="s">
         <v>29</v>
       </c>
@@ -8160,7 +8162,7 @@
       <c r="D17" s="6"/>
     </row>
     <row r="18" spans="1:64" ht="15" x14ac:dyDescent="0.2">
-      <c r="A18" s="100"/>
+      <c r="A18" s="97"/>
       <c r="B18" s="57" t="s">
         <v>30</v>
       </c>
@@ -8170,7 +8172,7 @@
       <c r="D18" s="6"/>
     </row>
     <row r="19" spans="1:64" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="100"/>
+      <c r="A19" s="97"/>
       <c r="B19" s="57" t="s">
         <v>31</v>
       </c>
@@ -8180,7 +8182,7 @@
       <c r="D19" s="6"/>
     </row>
     <row r="20" spans="1:64" ht="30" x14ac:dyDescent="0.2">
-      <c r="A20" s="100"/>
+      <c r="A20" s="97"/>
       <c r="B20" s="57" t="s">
         <v>32</v>
       </c>
@@ -8190,7 +8192,7 @@
       <c r="D20" s="6"/>
     </row>
     <row r="21" spans="1:64" ht="30" x14ac:dyDescent="0.2">
-      <c r="A21" s="100" t="s">
+      <c r="A21" s="97" t="s">
         <v>33</v>
       </c>
       <c r="B21" s="57" t="s">
@@ -8202,7 +8204,7 @@
       <c r="D21" s="6"/>
     </row>
     <row r="22" spans="1:64" ht="30" x14ac:dyDescent="0.2">
-      <c r="A22" s="100"/>
+      <c r="A22" s="97"/>
       <c r="B22" s="57" t="s">
         <v>35</v>
       </c>
@@ -8212,7 +8214,7 @@
       <c r="D22" s="6"/>
     </row>
     <row r="23" spans="1:64" ht="15" x14ac:dyDescent="0.2">
-      <c r="A23" s="100" t="s">
+      <c r="A23" s="97" t="s">
         <v>36</v>
       </c>
       <c r="B23" s="57" t="s">
@@ -8224,7 +8226,7 @@
       <c r="D23" s="6"/>
     </row>
     <row r="24" spans="1:64" ht="15" x14ac:dyDescent="0.2">
-      <c r="A24" s="100"/>
+      <c r="A24" s="97"/>
       <c r="B24" s="57" t="s">
         <v>38</v>
       </c>
@@ -8315,7 +8317,7 @@
       <c r="BL26" s="5"/>
     </row>
     <row r="27" spans="1:64" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A27" s="101" t="s">
+      <c r="A27" s="98" t="s">
         <v>41</v>
       </c>
       <c r="B27" s="31" t="s">
@@ -8386,7 +8388,7 @@
       <c r="BL27" s="5"/>
     </row>
     <row r="28" spans="1:64" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A28" s="102"/>
+      <c r="A28" s="99"/>
       <c r="B28" s="31" t="s">
         <v>99</v>
       </c>
@@ -8455,7 +8457,7 @@
       <c r="BL28" s="5"/>
     </row>
     <row r="29" spans="1:64" ht="15" x14ac:dyDescent="0.2">
-      <c r="A29" s="102"/>
+      <c r="A29" s="99"/>
       <c r="B29" s="57" t="s">
         <v>42</v>
       </c>
@@ -8465,7 +8467,7 @@
       <c r="D29" s="6"/>
     </row>
     <row r="30" spans="1:64" ht="15" x14ac:dyDescent="0.2">
-      <c r="A30" s="102"/>
+      <c r="A30" s="99"/>
       <c r="B30" s="57" t="s">
         <v>43</v>
       </c>
@@ -8475,7 +8477,7 @@
       <c r="D30" s="6"/>
     </row>
     <row r="31" spans="1:64" ht="15" x14ac:dyDescent="0.2">
-      <c r="A31" s="102"/>
+      <c r="A31" s="99"/>
       <c r="B31" s="57" t="s">
         <v>44</v>
       </c>
@@ -8485,7 +8487,7 @@
       <c r="D31" s="6"/>
     </row>
     <row r="32" spans="1:64" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="102"/>
+      <c r="A32" s="99"/>
       <c r="B32" s="57" t="s">
         <v>45</v>
       </c>
@@ -8495,7 +8497,7 @@
       <c r="D32" s="6"/>
     </row>
     <row r="33" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A33" s="103"/>
+      <c r="A33" s="100"/>
       <c r="B33" s="57" t="s">
         <v>46</v>
       </c>
@@ -8505,7 +8507,7 @@
       <c r="D33" s="6"/>
     </row>
     <row r="34" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A34" s="100" t="s">
+      <c r="A34" s="97" t="s">
         <v>47</v>
       </c>
       <c r="B34" s="57" t="s">
@@ -8517,7 +8519,7 @@
       <c r="D34" s="6"/>
     </row>
     <row r="35" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A35" s="100"/>
+      <c r="A35" s="97"/>
       <c r="B35" s="57" t="s">
         <v>49</v>
       </c>
@@ -8527,7 +8529,7 @@
       <c r="D35" s="6"/>
     </row>
     <row r="36" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A36" s="100" t="s">
+      <c r="A36" s="97" t="s">
         <v>50</v>
       </c>
       <c r="B36" s="57" t="s">
@@ -8539,7 +8541,7 @@
       <c r="D36" s="6"/>
     </row>
     <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A37" s="100"/>
+      <c r="A37" s="97"/>
       <c r="B37" s="57" t="s">
         <v>52</v>
       </c>
@@ -8549,7 +8551,7 @@
       <c r="D37" s="6"/>
     </row>
     <row r="38" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A38" s="100"/>
+      <c r="A38" s="97"/>
       <c r="B38" s="57" t="s">
         <v>53</v>
       </c>
@@ -8559,7 +8561,7 @@
       <c r="D38" s="6"/>
     </row>
     <row r="39" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A39" s="100"/>
+      <c r="A39" s="97"/>
       <c r="B39" s="57" t="s">
         <v>54</v>
       </c>
@@ -8569,7 +8571,7 @@
       <c r="D39" s="6"/>
     </row>
     <row r="40" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A40" s="100"/>
+      <c r="A40" s="97"/>
       <c r="B40" s="57" t="s">
         <v>55</v>
       </c>
@@ -8579,7 +8581,7 @@
       <c r="D40" s="6"/>
     </row>
     <row r="41" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A41" s="100" t="s">
+      <c r="A41" s="97" t="s">
         <v>56</v>
       </c>
       <c r="B41" s="57" t="s">
@@ -8591,7 +8593,7 @@
       <c r="D41" s="6"/>
     </row>
     <row r="42" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A42" s="100"/>
+      <c r="A42" s="97"/>
       <c r="B42" s="57" t="s">
         <v>58</v>
       </c>
@@ -8601,7 +8603,7 @@
       <c r="D42" s="6"/>
     </row>
     <row r="43" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A43" s="100"/>
+      <c r="A43" s="97"/>
       <c r="B43" s="57" t="s">
         <v>59</v>
       </c>
@@ -8611,7 +8613,7 @@
       <c r="D43" s="6"/>
     </row>
     <row r="44" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A44" s="100"/>
+      <c r="A44" s="97"/>
       <c r="B44" s="57" t="s">
         <v>60</v>
       </c>
@@ -8621,7 +8623,7 @@
       <c r="D44" s="6"/>
     </row>
     <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A45" s="100"/>
+      <c r="A45" s="97"/>
       <c r="B45" s="57" t="s">
         <v>61</v>
       </c>
@@ -8631,7 +8633,7 @@
       <c r="D45" s="6"/>
     </row>
     <row r="46" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A46" s="100"/>
+      <c r="A46" s="97"/>
       <c r="B46" s="57" t="s">
         <v>62</v>
       </c>
@@ -8641,7 +8643,7 @@
       <c r="D46" s="6"/>
     </row>
     <row r="47" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A47" s="100"/>
+      <c r="A47" s="97"/>
       <c r="B47" s="57" t="s">
         <v>63</v>
       </c>
@@ -8651,7 +8653,7 @@
       <c r="D47" s="6"/>
     </row>
     <row r="48" spans="1:4" ht="45" x14ac:dyDescent="0.2">
-      <c r="A48" s="100" t="s">
+      <c r="A48" s="97" t="s">
         <v>64</v>
       </c>
       <c r="B48" s="57" t="s">
@@ -8663,7 +8665,7 @@
       <c r="D48" s="6"/>
     </row>
     <row r="49" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A49" s="100"/>
+      <c r="A49" s="97"/>
       <c r="B49" s="57" t="s">
         <v>66</v>
       </c>
@@ -8673,7 +8675,7 @@
       <c r="D49" s="6"/>
     </row>
     <row r="50" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A50" s="100"/>
+      <c r="A50" s="97"/>
       <c r="B50" s="57" t="s">
         <v>67</v>
       </c>
@@ -8683,7 +8685,7 @@
       <c r="D50" s="6"/>
     </row>
     <row r="51" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A51" s="100"/>
+      <c r="A51" s="97"/>
       <c r="B51" s="57" t="s">
         <v>68</v>
       </c>
@@ -8693,7 +8695,7 @@
       <c r="D51" s="6"/>
     </row>
     <row r="52" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A52" s="100"/>
+      <c r="A52" s="97"/>
       <c r="B52" s="57" t="s">
         <v>69</v>
       </c>
@@ -8703,7 +8705,7 @@
       <c r="D52" s="6"/>
     </row>
     <row r="53" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A53" s="100" t="s">
+      <c r="A53" s="97" t="s">
         <v>70</v>
       </c>
       <c r="B53" s="57" t="s">
@@ -8715,7 +8717,7 @@
       <c r="D53" s="6"/>
     </row>
     <row r="54" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A54" s="100"/>
+      <c r="A54" s="97"/>
       <c r="B54" s="57" t="s">
         <v>72</v>
       </c>
@@ -8725,7 +8727,7 @@
       <c r="D54" s="6"/>
     </row>
     <row r="55" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A55" s="100"/>
+      <c r="A55" s="97"/>
       <c r="B55" s="57" t="s">
         <v>73</v>
       </c>
@@ -8736,6 +8738,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A20"/>
+    <mergeCell ref="A36:A40"/>
     <mergeCell ref="A41:A47"/>
     <mergeCell ref="A48:A52"/>
     <mergeCell ref="A53:A55"/>
@@ -8743,11 +8750,6 @@
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="A34:A35"/>
     <mergeCell ref="A27:A33"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:A9"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A20"/>
-    <mergeCell ref="A36:A40"/>
   </mergeCells>
   <pageMargins left="0.39374999999999999" right="0.39374999999999999" top="0.53263888888888899" bottom="0.39374999999999999" header="0.39374999999999999" footer="0.39374999999999999"/>
   <pageSetup scale="74" pageOrder="overThenDown" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -9633,7 +9635,7 @@
       <c r="BL3" s="2"/>
     </row>
     <row r="4" spans="1:1023" ht="30" x14ac:dyDescent="0.2">
-      <c r="A4" s="108" t="str">
+      <c r="A4" s="109" t="str">
         <f>Critères!$A$3</f>
         <v>IMAGES</v>
       </c>
@@ -9714,7 +9716,7 @@
       <c r="BL4" s="2"/>
     </row>
     <row r="5" spans="1:1023" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="108"/>
+      <c r="A5" s="109"/>
       <c r="B5" s="46" t="str">
         <f>Critères!B4</f>
         <v>1.2</v>
@@ -9798,7 +9800,7 @@
       <c r="AMI5" s="14"/>
     </row>
     <row r="6" spans="1:1023" ht="45" x14ac:dyDescent="0.2">
-      <c r="A6" s="108"/>
+      <c r="A6" s="109"/>
       <c r="B6" s="46" t="str">
         <f>Critères!B5</f>
         <v>1.3</v>
@@ -9876,7 +9878,7 @@
       <c r="BL6" s="2"/>
     </row>
     <row r="7" spans="1:1023" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="108"/>
+      <c r="A7" s="109"/>
       <c r="B7" s="46" t="str">
         <f>Critères!B6</f>
         <v>1.4</v>
@@ -9897,7 +9899,7 @@
       <c r="G7" s="32"/>
     </row>
     <row r="8" spans="1:1023" ht="45" x14ac:dyDescent="0.2">
-      <c r="A8" s="108"/>
+      <c r="A8" s="109"/>
       <c r="B8" s="46" t="str">
         <f>Critères!B7</f>
         <v>1.5</v>
@@ -9918,7 +9920,7 @@
       <c r="G8" s="32"/>
     </row>
     <row r="9" spans="1:1023" ht="30" x14ac:dyDescent="0.2">
-      <c r="A9" s="108"/>
+      <c r="A9" s="109"/>
       <c r="B9" s="46" t="str">
         <f>Critères!B8</f>
         <v>1.6</v>
@@ -9939,7 +9941,7 @@
       <c r="G9" s="32"/>
     </row>
     <row r="10" spans="1:1023" ht="45" x14ac:dyDescent="0.2">
-      <c r="A10" s="100"/>
+      <c r="A10" s="97"/>
       <c r="B10" s="75" t="str">
         <f>Critères!B9</f>
         <v>1.7</v>
@@ -9984,7 +9986,7 @@
       <c r="G11" s="82"/>
     </row>
     <row r="12" spans="1:1023" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="102" t="str">
+      <c r="A12" s="99" t="str">
         <f>Critères!$A$11</f>
         <v>COULEURS</v>
       </c>
@@ -10008,7 +10010,7 @@
       <c r="G12" s="78"/>
     </row>
     <row r="13" spans="1:1023" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="100"/>
+      <c r="A13" s="97"/>
       <c r="B13" s="75" t="str">
         <f>Critères!B12</f>
         <v>3.2</v>
@@ -10027,7 +10029,7 @@
       <c r="G13" s="76"/>
     </row>
     <row r="14" spans="1:1023" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="106" t="str">
+      <c r="A14" s="108" t="str">
         <f>Critères!$A$13</f>
         <v>MULTIMÉDIA</v>
       </c>
@@ -10051,7 +10053,7 @@
       <c r="G14" s="85"/>
     </row>
     <row r="15" spans="1:1023" ht="60" x14ac:dyDescent="0.2">
-      <c r="A15" s="108"/>
+      <c r="A15" s="109"/>
       <c r="B15" s="46" t="str">
         <f>Critères!B14</f>
         <v>4.2</v>
@@ -10072,7 +10074,7 @@
       <c r="G15" s="32"/>
     </row>
     <row r="16" spans="1:1023" ht="45" x14ac:dyDescent="0.2">
-      <c r="A16" s="108"/>
+      <c r="A16" s="109"/>
       <c r="B16" s="46" t="str">
         <f>Critères!B15</f>
         <v>4.3</v>
@@ -10093,7 +10095,7 @@
       <c r="G16" s="32"/>
     </row>
     <row r="17" spans="1:64" ht="45" x14ac:dyDescent="0.2">
-      <c r="A17" s="108"/>
+      <c r="A17" s="109"/>
       <c r="B17" s="46" t="str">
         <f>Critères!B16</f>
         <v>4.4</v>
@@ -10114,7 +10116,7 @@
       <c r="G17" s="32"/>
     </row>
     <row r="18" spans="1:64" ht="30" x14ac:dyDescent="0.2">
-      <c r="A18" s="108"/>
+      <c r="A18" s="109"/>
       <c r="B18" s="46" t="str">
         <f>Critères!B17</f>
         <v>4.8</v>
@@ -10135,7 +10137,7 @@
       <c r="G18" s="32"/>
     </row>
     <row r="19" spans="1:64" ht="30" x14ac:dyDescent="0.2">
-      <c r="A19" s="108"/>
+      <c r="A19" s="109"/>
       <c r="B19" s="46" t="str">
         <f>Critères!B18</f>
         <v>4.9</v>
@@ -10156,7 +10158,7 @@
       <c r="G19" s="32"/>
     </row>
     <row r="20" spans="1:64" ht="30" x14ac:dyDescent="0.2">
-      <c r="A20" s="108"/>
+      <c r="A20" s="109"/>
       <c r="B20" s="46" t="str">
         <f>Critères!B19</f>
         <v>4.10</v>
@@ -10177,7 +10179,7 @@
       <c r="G20" s="32"/>
     </row>
     <row r="21" spans="1:64" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="107"/>
+      <c r="A21" s="110"/>
       <c r="B21" s="87" t="str">
         <f>Critères!B20</f>
         <v>4.11</v>
@@ -10198,7 +10200,7 @@
       <c r="G21" s="88"/>
     </row>
     <row r="22" spans="1:64" ht="45" x14ac:dyDescent="0.2">
-      <c r="A22" s="106" t="s">
+      <c r="A22" s="108" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="84" t="str">
@@ -10221,7 +10223,7 @@
       <c r="G22" s="85"/>
     </row>
     <row r="23" spans="1:64" ht="45" x14ac:dyDescent="0.2">
-      <c r="A23" s="107"/>
+      <c r="A23" s="110"/>
       <c r="B23" s="87" t="str">
         <f>Critères!B22</f>
         <v>5.7</v>
@@ -10242,7 +10244,7 @@
       <c r="G23" s="88"/>
     </row>
     <row r="24" spans="1:64" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="106" t="str">
+      <c r="A24" s="108" t="str">
         <f>Critères!$A$23</f>
         <v>LIENS</v>
       </c>
@@ -10264,7 +10266,7 @@
       <c r="G24" s="85"/>
     </row>
     <row r="25" spans="1:64" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="107"/>
+      <c r="A25" s="110"/>
       <c r="B25" s="87" t="str">
         <f>Critères!B24</f>
         <v>6.2</v>
@@ -10308,7 +10310,7 @@
       <c r="G26" s="82"/>
     </row>
     <row r="27" spans="1:64" s="71" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A27" s="109" t="s">
+      <c r="A27" s="106" t="s">
         <v>113</v>
       </c>
       <c r="B27" s="84">
@@ -10387,7 +10389,7 @@
       <c r="BL27" s="5"/>
     </row>
     <row r="28" spans="1:64" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A28" s="101"/>
+      <c r="A28" s="98"/>
       <c r="B28" s="46" t="str">
         <f>Critères!B27</f>
         <v>8.2</v>
@@ -10465,7 +10467,7 @@
       <c r="BL28" s="5"/>
     </row>
     <row r="29" spans="1:64" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A29" s="101"/>
+      <c r="A29" s="98"/>
       <c r="B29" s="46" t="str">
         <f>Critères!B28</f>
         <v>8.3</v>
@@ -10543,7 +10545,7 @@
       <c r="BL29" s="5"/>
     </row>
     <row r="30" spans="1:64" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="101"/>
+      <c r="A30" s="98"/>
       <c r="B30" s="46" t="str">
         <f>Critères!B29</f>
         <v>8.4</v>
@@ -10564,7 +10566,7 @@
       <c r="G30" s="32"/>
     </row>
     <row r="31" spans="1:64" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="101"/>
+      <c r="A31" s="98"/>
       <c r="B31" s="46" t="str">
         <f>Critères!B30</f>
         <v>8.5</v>
@@ -10585,7 +10587,7 @@
       <c r="G31" s="32"/>
     </row>
     <row r="32" spans="1:64" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="101"/>
+      <c r="A32" s="98"/>
       <c r="B32" s="46" t="str">
         <f>Critères!B31</f>
         <v>8.6</v>
@@ -10606,7 +10608,7 @@
       <c r="G32" s="32"/>
     </row>
     <row r="33" spans="1:7" ht="45" x14ac:dyDescent="0.2">
-      <c r="A33" s="101"/>
+      <c r="A33" s="98"/>
       <c r="B33" s="46" t="str">
         <f>Critères!B32</f>
         <v>8.7</v>
@@ -10627,7 +10629,7 @@
       <c r="G33" s="32"/>
     </row>
     <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A34" s="110"/>
+      <c r="A34" s="107"/>
       <c r="B34" s="87" t="str">
         <f>Critères!B33</f>
         <v>8.8</v>
@@ -10648,7 +10650,7 @@
       <c r="G34" s="88"/>
     </row>
     <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A35" s="106" t="str">
+      <c r="A35" s="108" t="str">
         <f>Critères!$A$34</f>
         <v>STRUCTURATION</v>
       </c>
@@ -10670,7 +10672,7 @@
       <c r="G35" s="85"/>
     </row>
     <row r="36" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A36" s="107"/>
+      <c r="A36" s="110"/>
       <c r="B36" s="87" t="str">
         <f>Critères!B35</f>
         <v>9.2</v>
@@ -10691,7 +10693,7 @@
       <c r="G36" s="88"/>
     </row>
     <row r="37" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A37" s="106" t="s">
+      <c r="A37" s="108" t="s">
         <v>114</v>
       </c>
       <c r="B37" s="84" t="str">
@@ -10714,7 +10716,7 @@
       <c r="G37" s="85"/>
     </row>
     <row r="38" spans="1:7" ht="45" x14ac:dyDescent="0.2">
-      <c r="A38" s="108"/>
+      <c r="A38" s="109"/>
       <c r="B38" s="46" t="str">
         <f>Critères!B37</f>
         <v>10.8</v>
@@ -10735,7 +10737,7 @@
       <c r="G38" s="32"/>
     </row>
     <row r="39" spans="1:7" ht="45" x14ac:dyDescent="0.2">
-      <c r="A39" s="108"/>
+      <c r="A39" s="109"/>
       <c r="B39" s="46" t="str">
         <f>Critères!B38</f>
         <v>10.9</v>
@@ -10756,7 +10758,7 @@
       <c r="G39" s="32"/>
     </row>
     <row r="40" spans="1:7" ht="45" x14ac:dyDescent="0.2">
-      <c r="A40" s="108"/>
+      <c r="A40" s="109"/>
       <c r="B40" s="46" t="str">
         <f>Critères!B39</f>
         <v>10.10</v>
@@ -10777,7 +10779,7 @@
       <c r="G40" s="32"/>
     </row>
     <row r="41" spans="1:7" ht="60" x14ac:dyDescent="0.2">
-      <c r="A41" s="107"/>
+      <c r="A41" s="110"/>
       <c r="B41" s="87" t="str">
         <f>Critères!B40</f>
         <v>10.14</v>
@@ -10798,7 +10800,7 @@
       <c r="G41" s="88"/>
     </row>
     <row r="42" spans="1:7" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A42" s="106" t="str">
+      <c r="A42" s="108" t="str">
         <f>Critères!$A$41</f>
         <v>FORMULAIRES</v>
       </c>
@@ -10822,7 +10824,7 @@
       <c r="G42" s="85"/>
     </row>
     <row r="43" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A43" s="108"/>
+      <c r="A43" s="109"/>
       <c r="B43" s="46" t="str">
         <f>Critères!B42</f>
         <v>11.2</v>
@@ -10843,7 +10845,7 @@
       <c r="G43" s="32"/>
     </row>
     <row r="44" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A44" s="108"/>
+      <c r="A44" s="109"/>
       <c r="B44" s="46" t="str">
         <f>Critères!B43</f>
         <v>11.5</v>
@@ -10864,7 +10866,7 @@
       <c r="G44" s="32"/>
     </row>
     <row r="45" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A45" s="108"/>
+      <c r="A45" s="109"/>
       <c r="B45" s="46" t="str">
         <f>Critères!B44</f>
         <v>11.6</v>
@@ -10885,7 +10887,7 @@
       <c r="G45" s="32"/>
     </row>
     <row r="46" spans="1:7" ht="45" x14ac:dyDescent="0.2">
-      <c r="A46" s="108"/>
+      <c r="A46" s="109"/>
       <c r="B46" s="46" t="str">
         <f>Critères!B45</f>
         <v>11.7</v>
@@ -10906,7 +10908,7 @@
       <c r="G46" s="32"/>
     </row>
     <row r="47" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A47" s="108"/>
+      <c r="A47" s="109"/>
       <c r="B47" s="46" t="str">
         <f>Critères!B46</f>
         <v>11.9</v>
@@ -10927,7 +10929,7 @@
       <c r="G47" s="32"/>
     </row>
     <row r="48" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A48" s="107"/>
+      <c r="A48" s="110"/>
       <c r="B48" s="87" t="str">
         <f>Critères!B47</f>
         <v>11.10</v>
@@ -10948,7 +10950,7 @@
       <c r="G48" s="88"/>
     </row>
     <row r="49" spans="1:7" ht="75" x14ac:dyDescent="0.2">
-      <c r="A49" s="106" t="s">
+      <c r="A49" s="108" t="s">
         <v>64</v>
       </c>
       <c r="B49" s="84" t="str">
@@ -10971,7 +10973,7 @@
       <c r="G49" s="85"/>
     </row>
     <row r="50" spans="1:7" ht="45" x14ac:dyDescent="0.2">
-      <c r="A50" s="108"/>
+      <c r="A50" s="109"/>
       <c r="B50" s="46" t="str">
         <f>Critères!B49</f>
         <v>12.7</v>
@@ -10992,7 +10994,7 @@
       <c r="G50" s="32"/>
     </row>
     <row r="51" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A51" s="108"/>
+      <c r="A51" s="109"/>
       <c r="B51" s="46" t="str">
         <f>Critères!B50</f>
         <v>12.8</v>
@@ -11013,7 +11015,7 @@
       <c r="G51" s="32"/>
     </row>
     <row r="52" spans="1:7" ht="45" x14ac:dyDescent="0.2">
-      <c r="A52" s="108"/>
+      <c r="A52" s="109"/>
       <c r="B52" s="46" t="str">
         <f>Critères!B51</f>
         <v>12.9</v>
@@ -11034,7 +11036,7 @@
       <c r="G52" s="32"/>
     </row>
     <row r="53" spans="1:7" ht="60" x14ac:dyDescent="0.2">
-      <c r="A53" s="107"/>
+      <c r="A53" s="110"/>
       <c r="B53" s="87" t="str">
         <f>Critères!B52</f>
         <v>12.11</v>
@@ -11053,7 +11055,7 @@
       <c r="G53" s="88"/>
     </row>
     <row r="54" spans="1:7" ht="45" x14ac:dyDescent="0.2">
-      <c r="A54" s="106" t="str">
+      <c r="A54" s="108" t="str">
         <f>Critères!$A$53</f>
         <v>CONSULTATION</v>
       </c>
@@ -11077,7 +11079,7 @@
       <c r="G54" s="85"/>
     </row>
     <row r="55" spans="1:7" ht="45" x14ac:dyDescent="0.2">
-      <c r="A55" s="108"/>
+      <c r="A55" s="109"/>
       <c r="B55" s="46" t="str">
         <f>Critères!B54</f>
         <v>13.7</v>
@@ -11098,7 +11100,7 @@
       <c r="G55" s="32"/>
     </row>
     <row r="56" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A56" s="107"/>
+      <c r="A56" s="110"/>
       <c r="B56" s="87" t="str">
         <f>Critères!B55</f>
         <v>13.8</v>
@@ -11120,6 +11122,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="A42:A48"/>
+    <mergeCell ref="A49:A53"/>
+    <mergeCell ref="A54:A56"/>
     <mergeCell ref="A27:A34"/>
     <mergeCell ref="A14:A21"/>
     <mergeCell ref="A22:A23"/>
@@ -11128,11 +11135,6 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A4:A10"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:A41"/>
-    <mergeCell ref="A42:A48"/>
-    <mergeCell ref="A49:A53"/>
-    <mergeCell ref="A54:A56"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D56">
     <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
@@ -11295,7 +11297,7 @@
       <c r="BL3" s="48"/>
     </row>
     <row r="4" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A4" s="106" t="str">
+      <c r="A4" s="108" t="str">
         <f>Critères!$A$3</f>
         <v>IMAGES</v>
       </c>
@@ -11375,7 +11377,7 @@
       <c r="BL4" s="48"/>
     </row>
     <row r="5" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="108"/>
+      <c r="A5" s="109"/>
       <c r="B5" s="46" t="str">
         <f>Critères!B4</f>
         <v>1.2</v>
@@ -11453,7 +11455,7 @@
       <c r="BL5" s="48"/>
     </row>
     <row r="6" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A6" s="108"/>
+      <c r="A6" s="109"/>
       <c r="B6" s="46" t="str">
         <f>Critères!B5</f>
         <v>1.3</v>
@@ -11531,7 +11533,7 @@
       <c r="BL6" s="48"/>
     </row>
     <row r="7" spans="1:64" s="49" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="108"/>
+      <c r="A7" s="109"/>
       <c r="B7" s="46" t="str">
         <f>Critères!B6</f>
         <v>1.4</v>
@@ -11609,7 +11611,7 @@
       <c r="BL7" s="48"/>
     </row>
     <row r="8" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A8" s="108"/>
+      <c r="A8" s="109"/>
       <c r="B8" s="46" t="str">
         <f>Critères!B7</f>
         <v>1.5</v>
@@ -11687,7 +11689,7 @@
       <c r="BL8" s="48"/>
     </row>
     <row r="9" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A9" s="108"/>
+      <c r="A9" s="109"/>
       <c r="B9" s="46" t="str">
         <f>Critères!B8</f>
         <v>1.6</v>
@@ -11765,7 +11767,7 @@
       <c r="BL9" s="48"/>
     </row>
     <row r="10" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A10" s="107"/>
+      <c r="A10" s="110"/>
       <c r="B10" s="87" t="str">
         <f>Critères!B9</f>
         <v>1.7</v>
@@ -11924,7 +11926,7 @@
       <c r="BL11" s="48"/>
     </row>
     <row r="12" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="106" t="str">
+      <c r="A12" s="108" t="str">
         <f>Critères!$A$11</f>
         <v>COULEURS</v>
       </c>
@@ -12005,7 +12007,7 @@
       <c r="BL12" s="48"/>
     </row>
     <row r="13" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="107"/>
+      <c r="A13" s="110"/>
       <c r="B13" s="87" t="str">
         <f>Critères!B12</f>
         <v>3.2</v>
@@ -12083,7 +12085,7 @@
       <c r="BL13" s="48"/>
     </row>
     <row r="14" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="106" t="str">
+      <c r="A14" s="108" t="str">
         <f>Critères!$A$13</f>
         <v>MULTIMÉDIA</v>
       </c>
@@ -12164,7 +12166,7 @@
       <c r="BL14" s="48"/>
     </row>
     <row r="15" spans="1:64" s="49" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A15" s="108"/>
+      <c r="A15" s="109"/>
       <c r="B15" s="46" t="str">
         <f>Critères!B14</f>
         <v>4.2</v>
@@ -12242,7 +12244,7 @@
       <c r="BL15" s="48"/>
     </row>
     <row r="16" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A16" s="108"/>
+      <c r="A16" s="109"/>
       <c r="B16" s="46" t="str">
         <f>Critères!B15</f>
         <v>4.3</v>
@@ -12320,7 +12322,7 @@
       <c r="BL16" s="48"/>
     </row>
     <row r="17" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A17" s="108"/>
+      <c r="A17" s="109"/>
       <c r="B17" s="46" t="str">
         <f>Critères!B16</f>
         <v>4.4</v>
@@ -12398,7 +12400,7 @@
       <c r="BL17" s="48"/>
     </row>
     <row r="18" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A18" s="108"/>
+      <c r="A18" s="109"/>
       <c r="B18" s="46" t="str">
         <f>Critères!B17</f>
         <v>4.8</v>
@@ -12476,7 +12478,7 @@
       <c r="BL18" s="48"/>
     </row>
     <row r="19" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A19" s="108"/>
+      <c r="A19" s="109"/>
       <c r="B19" s="46" t="str">
         <f>Critères!B18</f>
         <v>4.9</v>
@@ -12554,7 +12556,7 @@
       <c r="BL19" s="48"/>
     </row>
     <row r="20" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A20" s="108"/>
+      <c r="A20" s="109"/>
       <c r="B20" s="46" t="str">
         <f>Critères!B19</f>
         <v>4.10</v>
@@ -12632,7 +12634,7 @@
       <c r="BL20" s="48"/>
     </row>
     <row r="21" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="107"/>
+      <c r="A21" s="110"/>
       <c r="B21" s="87" t="str">
         <f>Critères!B20</f>
         <v>4.11</v>
@@ -12710,7 +12712,7 @@
       <c r="BL21" s="48"/>
     </row>
     <row r="22" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A22" s="106" t="s">
+      <c r="A22" s="108" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="84" t="str">
@@ -12790,7 +12792,7 @@
       <c r="BL22" s="48"/>
     </row>
     <row r="23" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A23" s="107"/>
+      <c r="A23" s="110"/>
       <c r="B23" s="87" t="str">
         <f>Critères!B22</f>
         <v>5.7</v>
@@ -12868,7 +12870,7 @@
       <c r="BL23" s="48"/>
     </row>
     <row r="24" spans="1:64" s="49" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="106" t="str">
+      <c r="A24" s="108" t="str">
         <f>Critères!$A$23</f>
         <v>LIENS</v>
       </c>
@@ -12949,7 +12951,7 @@
       <c r="BL24" s="48"/>
     </row>
     <row r="25" spans="1:64" s="49" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="107"/>
+      <c r="A25" s="110"/>
       <c r="B25" s="87" t="str">
         <f>Critères!B24</f>
         <v>6.2</v>
@@ -13107,7 +13109,7 @@
       <c r="BL26" s="48"/>
     </row>
     <row r="27" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A27" s="109" t="s">
+      <c r="A27" s="106" t="s">
         <v>113</v>
       </c>
       <c r="B27" s="84">
@@ -13186,7 +13188,7 @@
       <c r="BL27" s="48"/>
     </row>
     <row r="28" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A28" s="101"/>
+      <c r="A28" s="98"/>
       <c r="B28" s="46" t="str">
         <f>Critères!B27</f>
         <v>8.2</v>
@@ -13264,7 +13266,7 @@
       <c r="BL28" s="48"/>
     </row>
     <row r="29" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A29" s="101"/>
+      <c r="A29" s="98"/>
       <c r="B29" s="46" t="str">
         <f>Critères!B28</f>
         <v>8.3</v>
@@ -13342,7 +13344,7 @@
       <c r="BL29" s="48"/>
     </row>
     <row r="30" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="101"/>
+      <c r="A30" s="98"/>
       <c r="B30" s="46" t="str">
         <f>Critères!B29</f>
         <v>8.4</v>
@@ -13420,7 +13422,7 @@
       <c r="BL30" s="48"/>
     </row>
     <row r="31" spans="1:64" s="49" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="101"/>
+      <c r="A31" s="98"/>
       <c r="B31" s="46" t="str">
         <f>Critères!B30</f>
         <v>8.5</v>
@@ -13498,7 +13500,7 @@
       <c r="BL31" s="48"/>
     </row>
     <row r="32" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="101"/>
+      <c r="A32" s="98"/>
       <c r="B32" s="46" t="str">
         <f>Critères!B31</f>
         <v>8.6</v>
@@ -13576,7 +13578,7 @@
       <c r="BL32" s="48"/>
     </row>
     <row r="33" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A33" s="101"/>
+      <c r="A33" s="98"/>
       <c r="B33" s="46" t="str">
         <f>Critères!B32</f>
         <v>8.7</v>
@@ -13654,7 +13656,7 @@
       <c r="BL33" s="48"/>
     </row>
     <row r="34" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A34" s="101"/>
+      <c r="A34" s="98"/>
       <c r="B34" s="75" t="str">
         <f>Critères!B33</f>
         <v>8.8</v>
@@ -13732,7 +13734,7 @@
       <c r="BL34" s="48"/>
     </row>
     <row r="35" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A35" s="106" t="str">
+      <c r="A35" s="108" t="str">
         <f>Critères!$A$34</f>
         <v>STRUCTURATION</v>
       </c>
@@ -13813,7 +13815,7 @@
       <c r="BL35" s="48"/>
     </row>
     <row r="36" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A36" s="107"/>
+      <c r="A36" s="110"/>
       <c r="B36" s="87" t="str">
         <f>Critères!B35</f>
         <v>9.2</v>
@@ -13891,7 +13893,7 @@
       <c r="BL36" s="48"/>
     </row>
     <row r="37" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A37" s="106" t="s">
+      <c r="A37" s="108" t="s">
         <v>114</v>
       </c>
       <c r="B37" s="84" t="str">
@@ -13971,7 +13973,7 @@
       <c r="BL37" s="48"/>
     </row>
     <row r="38" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A38" s="108"/>
+      <c r="A38" s="109"/>
       <c r="B38" s="46" t="str">
         <f>Critères!B37</f>
         <v>10.8</v>
@@ -14049,7 +14051,7 @@
       <c r="BL38" s="48"/>
     </row>
     <row r="39" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A39" s="108"/>
+      <c r="A39" s="109"/>
       <c r="B39" s="46" t="str">
         <f>Critères!B38</f>
         <v>10.9</v>
@@ -14127,7 +14129,7 @@
       <c r="BL39" s="48"/>
     </row>
     <row r="40" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A40" s="108"/>
+      <c r="A40" s="109"/>
       <c r="B40" s="46" t="str">
         <f>Critères!B39</f>
         <v>10.10</v>
@@ -14205,7 +14207,7 @@
       <c r="BL40" s="48"/>
     </row>
     <row r="41" spans="1:64" s="49" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A41" s="107"/>
+      <c r="A41" s="110"/>
       <c r="B41" s="87" t="str">
         <f>Critères!B40</f>
         <v>10.14</v>
@@ -14283,7 +14285,7 @@
       <c r="BL41" s="48"/>
     </row>
     <row r="42" spans="1:64" s="49" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A42" s="106" t="str">
+      <c r="A42" s="108" t="str">
         <f>Critères!$A$41</f>
         <v>FORMULAIRES</v>
       </c>
@@ -14364,7 +14366,7 @@
       <c r="BL42" s="48"/>
     </row>
     <row r="43" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A43" s="108"/>
+      <c r="A43" s="109"/>
       <c r="B43" s="46" t="str">
         <f>Critères!B42</f>
         <v>11.2</v>
@@ -14442,7 +14444,7 @@
       <c r="BL43" s="48"/>
     </row>
     <row r="44" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A44" s="108"/>
+      <c r="A44" s="109"/>
       <c r="B44" s="46" t="str">
         <f>Critères!B43</f>
         <v>11.5</v>
@@ -14520,7 +14522,7 @@
       <c r="BL44" s="48"/>
     </row>
     <row r="45" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A45" s="108"/>
+      <c r="A45" s="109"/>
       <c r="B45" s="46" t="str">
         <f>Critères!B44</f>
         <v>11.6</v>
@@ -14598,7 +14600,7 @@
       <c r="BL45" s="48"/>
     </row>
     <row r="46" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A46" s="108"/>
+      <c r="A46" s="109"/>
       <c r="B46" s="46" t="str">
         <f>Critères!B45</f>
         <v>11.7</v>
@@ -14676,7 +14678,7 @@
       <c r="BL46" s="48"/>
     </row>
     <row r="47" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A47" s="108"/>
+      <c r="A47" s="109"/>
       <c r="B47" s="46" t="str">
         <f>Critères!B46</f>
         <v>11.9</v>
@@ -14754,7 +14756,7 @@
       <c r="BL47" s="48"/>
     </row>
     <row r="48" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A48" s="107"/>
+      <c r="A48" s="110"/>
       <c r="B48" s="87" t="str">
         <f>Critères!B47</f>
         <v>11.10</v>
@@ -14832,7 +14834,7 @@
       <c r="BL48" s="48"/>
     </row>
     <row r="49" spans="1:64" s="49" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A49" s="106" t="s">
+      <c r="A49" s="108" t="s">
         <v>64</v>
       </c>
       <c r="B49" s="84" t="str">
@@ -14912,7 +14914,7 @@
       <c r="BL49" s="48"/>
     </row>
     <row r="50" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A50" s="108"/>
+      <c r="A50" s="109"/>
       <c r="B50" s="46" t="str">
         <f>Critères!B49</f>
         <v>12.7</v>
@@ -14990,7 +14992,7 @@
       <c r="BL50" s="48"/>
     </row>
     <row r="51" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A51" s="108"/>
+      <c r="A51" s="109"/>
       <c r="B51" s="46" t="str">
         <f>Critères!B50</f>
         <v>12.8</v>
@@ -15068,7 +15070,7 @@
       <c r="BL51" s="48"/>
     </row>
     <row r="52" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A52" s="108"/>
+      <c r="A52" s="109"/>
       <c r="B52" s="46" t="str">
         <f>Critères!B51</f>
         <v>12.9</v>
@@ -15146,7 +15148,7 @@
       <c r="BL52" s="48"/>
     </row>
     <row r="53" spans="1:64" s="49" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A53" s="107"/>
+      <c r="A53" s="110"/>
       <c r="B53" s="87" t="str">
         <f>Critères!B52</f>
         <v>12.11</v>
@@ -15224,7 +15226,7 @@
       <c r="BL53" s="48"/>
     </row>
     <row r="54" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A54" s="106" t="str">
+      <c r="A54" s="108" t="str">
         <f>Critères!$A$53</f>
         <v>CONSULTATION</v>
       </c>
@@ -15305,7 +15307,7 @@
       <c r="BL54" s="48"/>
     </row>
     <row r="55" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A55" s="108"/>
+      <c r="A55" s="109"/>
       <c r="B55" s="46" t="str">
         <f>Critères!B54</f>
         <v>13.7</v>
@@ -15383,7 +15385,7 @@
       <c r="BL55" s="48"/>
     </row>
     <row r="56" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A56" s="107"/>
+      <c r="A56" s="110"/>
       <c r="B56" s="87" t="str">
         <f>Critères!B55</f>
         <v>13.8</v>
@@ -15462,6 +15464,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A27:A34"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="A42:A48"/>
+    <mergeCell ref="A49:A53"/>
     <mergeCell ref="A14:A21"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="A24:A25"/>
@@ -15469,12 +15477,6 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A4:A10"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A27:A34"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:A41"/>
-    <mergeCell ref="A42:A48"/>
-    <mergeCell ref="A49:A53"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D56">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -15637,7 +15639,7 @@
       <c r="BL3" s="48"/>
     </row>
     <row r="4" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A4" s="106" t="str">
+      <c r="A4" s="108" t="str">
         <f>Critères!$A$3</f>
         <v>IMAGES</v>
       </c>
@@ -15717,7 +15719,7 @@
       <c r="BL4" s="48"/>
     </row>
     <row r="5" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="108"/>
+      <c r="A5" s="109"/>
       <c r="B5" s="46" t="str">
         <f>Critères!B4</f>
         <v>1.2</v>
@@ -15795,7 +15797,7 @@
       <c r="BL5" s="48"/>
     </row>
     <row r="6" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A6" s="108"/>
+      <c r="A6" s="109"/>
       <c r="B6" s="46" t="str">
         <f>Critères!B5</f>
         <v>1.3</v>
@@ -15873,7 +15875,7 @@
       <c r="BL6" s="48"/>
     </row>
     <row r="7" spans="1:64" s="49" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="108"/>
+      <c r="A7" s="109"/>
       <c r="B7" s="46" t="str">
         <f>Critères!B6</f>
         <v>1.4</v>
@@ -15951,7 +15953,7 @@
       <c r="BL7" s="48"/>
     </row>
     <row r="8" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A8" s="108"/>
+      <c r="A8" s="109"/>
       <c r="B8" s="46" t="str">
         <f>Critères!B7</f>
         <v>1.5</v>
@@ -16029,7 +16031,7 @@
       <c r="BL8" s="48"/>
     </row>
     <row r="9" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A9" s="108"/>
+      <c r="A9" s="109"/>
       <c r="B9" s="46" t="str">
         <f>Critères!B8</f>
         <v>1.6</v>
@@ -16107,7 +16109,7 @@
       <c r="BL9" s="48"/>
     </row>
     <row r="10" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A10" s="107"/>
+      <c r="A10" s="110"/>
       <c r="B10" s="87" t="str">
         <f>Critères!B9</f>
         <v>1.7</v>
@@ -16266,7 +16268,7 @@
       <c r="BL11" s="48"/>
     </row>
     <row r="12" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="106" t="str">
+      <c r="A12" s="108" t="str">
         <f>Critères!$A$11</f>
         <v>COULEURS</v>
       </c>
@@ -16347,7 +16349,7 @@
       <c r="BL12" s="48"/>
     </row>
     <row r="13" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="107"/>
+      <c r="A13" s="110"/>
       <c r="B13" s="87" t="str">
         <f>Critères!B12</f>
         <v>3.2</v>
@@ -16425,7 +16427,7 @@
       <c r="BL13" s="48"/>
     </row>
     <row r="14" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="106" t="str">
+      <c r="A14" s="108" t="str">
         <f>Critères!$A$13</f>
         <v>MULTIMÉDIA</v>
       </c>
@@ -16506,7 +16508,7 @@
       <c r="BL14" s="48"/>
     </row>
     <row r="15" spans="1:64" s="49" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A15" s="108"/>
+      <c r="A15" s="109"/>
       <c r="B15" s="46" t="str">
         <f>Critères!B14</f>
         <v>4.2</v>
@@ -16584,7 +16586,7 @@
       <c r="BL15" s="48"/>
     </row>
     <row r="16" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A16" s="108"/>
+      <c r="A16" s="109"/>
       <c r="B16" s="46" t="str">
         <f>Critères!B15</f>
         <v>4.3</v>
@@ -16662,7 +16664,7 @@
       <c r="BL16" s="48"/>
     </row>
     <row r="17" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A17" s="108"/>
+      <c r="A17" s="109"/>
       <c r="B17" s="46" t="str">
         <f>Critères!B16</f>
         <v>4.4</v>
@@ -16740,7 +16742,7 @@
       <c r="BL17" s="48"/>
     </row>
     <row r="18" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A18" s="108"/>
+      <c r="A18" s="109"/>
       <c r="B18" s="46" t="str">
         <f>Critères!B17</f>
         <v>4.8</v>
@@ -16818,7 +16820,7 @@
       <c r="BL18" s="48"/>
     </row>
     <row r="19" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A19" s="108"/>
+      <c r="A19" s="109"/>
       <c r="B19" s="46" t="str">
         <f>Critères!B18</f>
         <v>4.9</v>
@@ -16896,7 +16898,7 @@
       <c r="BL19" s="48"/>
     </row>
     <row r="20" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A20" s="108"/>
+      <c r="A20" s="109"/>
       <c r="B20" s="46" t="str">
         <f>Critères!B19</f>
         <v>4.10</v>
@@ -16974,7 +16976,7 @@
       <c r="BL20" s="48"/>
     </row>
     <row r="21" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="107"/>
+      <c r="A21" s="110"/>
       <c r="B21" s="87" t="str">
         <f>Critères!B20</f>
         <v>4.11</v>
@@ -17052,7 +17054,7 @@
       <c r="BL21" s="48"/>
     </row>
     <row r="22" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A22" s="106" t="s">
+      <c r="A22" s="108" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="84" t="str">
@@ -17132,7 +17134,7 @@
       <c r="BL22" s="48"/>
     </row>
     <row r="23" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A23" s="107"/>
+      <c r="A23" s="110"/>
       <c r="B23" s="87" t="str">
         <f>Critères!B22</f>
         <v>5.7</v>
@@ -17210,7 +17212,7 @@
       <c r="BL23" s="48"/>
     </row>
     <row r="24" spans="1:64" s="49" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="106" t="str">
+      <c r="A24" s="108" t="str">
         <f>Critères!$A$23</f>
         <v>LIENS</v>
       </c>
@@ -17291,7 +17293,7 @@
       <c r="BL24" s="48"/>
     </row>
     <row r="25" spans="1:64" s="49" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="107"/>
+      <c r="A25" s="110"/>
       <c r="B25" s="87" t="str">
         <f>Critères!B24</f>
         <v>6.2</v>
@@ -17449,7 +17451,7 @@
       <c r="BL26" s="48"/>
     </row>
     <row r="27" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A27" s="109" t="s">
+      <c r="A27" s="106" t="s">
         <v>113</v>
       </c>
       <c r="B27" s="84">
@@ -17528,7 +17530,7 @@
       <c r="BL27" s="48"/>
     </row>
     <row r="28" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A28" s="101"/>
+      <c r="A28" s="98"/>
       <c r="B28" s="46" t="str">
         <f>Critères!B27</f>
         <v>8.2</v>
@@ -17606,7 +17608,7 @@
       <c r="BL28" s="48"/>
     </row>
     <row r="29" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A29" s="101"/>
+      <c r="A29" s="98"/>
       <c r="B29" s="46" t="str">
         <f>Critères!B28</f>
         <v>8.3</v>
@@ -17684,7 +17686,7 @@
       <c r="BL29" s="48"/>
     </row>
     <row r="30" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="101"/>
+      <c r="A30" s="98"/>
       <c r="B30" s="46" t="str">
         <f>Critères!B29</f>
         <v>8.4</v>
@@ -17762,7 +17764,7 @@
       <c r="BL30" s="48"/>
     </row>
     <row r="31" spans="1:64" s="49" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="101"/>
+      <c r="A31" s="98"/>
       <c r="B31" s="46" t="str">
         <f>Critères!B30</f>
         <v>8.5</v>
@@ -17840,7 +17842,7 @@
       <c r="BL31" s="48"/>
     </row>
     <row r="32" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="101"/>
+      <c r="A32" s="98"/>
       <c r="B32" s="46" t="str">
         <f>Critères!B31</f>
         <v>8.6</v>
@@ -17918,7 +17920,7 @@
       <c r="BL32" s="48"/>
     </row>
     <row r="33" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A33" s="101"/>
+      <c r="A33" s="98"/>
       <c r="B33" s="46" t="str">
         <f>Critères!B32</f>
         <v>8.7</v>
@@ -17996,7 +17998,7 @@
       <c r="BL33" s="48"/>
     </row>
     <row r="34" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A34" s="110"/>
+      <c r="A34" s="107"/>
       <c r="B34" s="87" t="str">
         <f>Critères!B33</f>
         <v>8.8</v>
@@ -18074,7 +18076,7 @@
       <c r="BL34" s="48"/>
     </row>
     <row r="35" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A35" s="106" t="str">
+      <c r="A35" s="108" t="str">
         <f>Critères!$A$34</f>
         <v>STRUCTURATION</v>
       </c>
@@ -18155,7 +18157,7 @@
       <c r="BL35" s="48"/>
     </row>
     <row r="36" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A36" s="107"/>
+      <c r="A36" s="110"/>
       <c r="B36" s="87" t="str">
         <f>Critères!B35</f>
         <v>9.2</v>
@@ -18233,7 +18235,7 @@
       <c r="BL36" s="48"/>
     </row>
     <row r="37" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A37" s="106" t="s">
+      <c r="A37" s="108" t="s">
         <v>114</v>
       </c>
       <c r="B37" s="84" t="str">
@@ -18313,7 +18315,7 @@
       <c r="BL37" s="48"/>
     </row>
     <row r="38" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A38" s="108"/>
+      <c r="A38" s="109"/>
       <c r="B38" s="46" t="str">
         <f>Critères!B37</f>
         <v>10.8</v>
@@ -18391,7 +18393,7 @@
       <c r="BL38" s="48"/>
     </row>
     <row r="39" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A39" s="108"/>
+      <c r="A39" s="109"/>
       <c r="B39" s="46" t="str">
         <f>Critères!B38</f>
         <v>10.9</v>
@@ -18469,7 +18471,7 @@
       <c r="BL39" s="48"/>
     </row>
     <row r="40" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A40" s="108"/>
+      <c r="A40" s="109"/>
       <c r="B40" s="46" t="str">
         <f>Critères!B39</f>
         <v>10.10</v>
@@ -18547,7 +18549,7 @@
       <c r="BL40" s="48"/>
     </row>
     <row r="41" spans="1:64" s="49" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A41" s="107"/>
+      <c r="A41" s="110"/>
       <c r="B41" s="87" t="str">
         <f>Critères!B40</f>
         <v>10.14</v>
@@ -18625,7 +18627,7 @@
       <c r="BL41" s="48"/>
     </row>
     <row r="42" spans="1:64" s="49" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A42" s="106" t="str">
+      <c r="A42" s="108" t="str">
         <f>Critères!$A$41</f>
         <v>FORMULAIRES</v>
       </c>
@@ -18706,7 +18708,7 @@
       <c r="BL42" s="48"/>
     </row>
     <row r="43" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A43" s="108"/>
+      <c r="A43" s="109"/>
       <c r="B43" s="46" t="str">
         <f>Critères!B42</f>
         <v>11.2</v>
@@ -18784,7 +18786,7 @@
       <c r="BL43" s="48"/>
     </row>
     <row r="44" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A44" s="108"/>
+      <c r="A44" s="109"/>
       <c r="B44" s="46" t="str">
         <f>Critères!B43</f>
         <v>11.5</v>
@@ -18862,7 +18864,7 @@
       <c r="BL44" s="48"/>
     </row>
     <row r="45" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A45" s="108"/>
+      <c r="A45" s="109"/>
       <c r="B45" s="46" t="str">
         <f>Critères!B44</f>
         <v>11.6</v>
@@ -18940,7 +18942,7 @@
       <c r="BL45" s="48"/>
     </row>
     <row r="46" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A46" s="108"/>
+      <c r="A46" s="109"/>
       <c r="B46" s="46" t="str">
         <f>Critères!B45</f>
         <v>11.7</v>
@@ -19018,7 +19020,7 @@
       <c r="BL46" s="48"/>
     </row>
     <row r="47" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A47" s="108"/>
+      <c r="A47" s="109"/>
       <c r="B47" s="46" t="str">
         <f>Critères!B46</f>
         <v>11.9</v>
@@ -19096,7 +19098,7 @@
       <c r="BL47" s="48"/>
     </row>
     <row r="48" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A48" s="107"/>
+      <c r="A48" s="110"/>
       <c r="B48" s="87" t="str">
         <f>Critères!B47</f>
         <v>11.10</v>
@@ -19174,7 +19176,7 @@
       <c r="BL48" s="48"/>
     </row>
     <row r="49" spans="1:64" s="49" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A49" s="106" t="s">
+      <c r="A49" s="108" t="s">
         <v>64</v>
       </c>
       <c r="B49" s="84" t="str">
@@ -19254,7 +19256,7 @@
       <c r="BL49" s="48"/>
     </row>
     <row r="50" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A50" s="108"/>
+      <c r="A50" s="109"/>
       <c r="B50" s="46" t="str">
         <f>Critères!B49</f>
         <v>12.7</v>
@@ -19332,7 +19334,7 @@
       <c r="BL50" s="48"/>
     </row>
     <row r="51" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A51" s="108"/>
+      <c r="A51" s="109"/>
       <c r="B51" s="46" t="str">
         <f>Critères!B50</f>
         <v>12.8</v>
@@ -19410,7 +19412,7 @@
       <c r="BL51" s="48"/>
     </row>
     <row r="52" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A52" s="108"/>
+      <c r="A52" s="109"/>
       <c r="B52" s="46" t="str">
         <f>Critères!B51</f>
         <v>12.9</v>
@@ -19488,7 +19490,7 @@
       <c r="BL52" s="48"/>
     </row>
     <row r="53" spans="1:64" s="49" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A53" s="107"/>
+      <c r="A53" s="110"/>
       <c r="B53" s="87" t="str">
         <f>Critères!B52</f>
         <v>12.11</v>
@@ -19566,7 +19568,7 @@
       <c r="BL53" s="48"/>
     </row>
     <row r="54" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A54" s="106" t="str">
+      <c r="A54" s="108" t="str">
         <f>Critères!$A$53</f>
         <v>CONSULTATION</v>
       </c>
@@ -19647,7 +19649,7 @@
       <c r="BL54" s="48"/>
     </row>
     <row r="55" spans="1:64" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A55" s="108"/>
+      <c r="A55" s="109"/>
       <c r="B55" s="46" t="str">
         <f>Critères!B54</f>
         <v>13.7</v>
@@ -19725,7 +19727,7 @@
       <c r="BL55" s="48"/>
     </row>
     <row r="56" spans="1:64" s="49" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A56" s="107"/>
+      <c r="A56" s="110"/>
       <c r="B56" s="87" t="str">
         <f>Critères!B55</f>
         <v>13.8</v>
@@ -19804,6 +19806,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A27:A34"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="A42:A48"/>
+    <mergeCell ref="A49:A53"/>
     <mergeCell ref="A14:A21"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="A24:A25"/>
@@ -19811,12 +19819,6 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A4:A10"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A27:A34"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:A41"/>
-    <mergeCell ref="A42:A48"/>
-    <mergeCell ref="A49:A53"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D56">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">

--- a/static/template-grille-audit-simplifie.xlsx
+++ b/static/template-grille-audit-simplifie.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ifi774\Projects\simplA11yMonit\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF26D2E-2D3F-41BF-AABC-AAD297546E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4C10C6-A3B0-47C2-B40E-6E8CBA425A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{091586B1-AD82-4EC5-8ABD-408E12CDFE42}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{091586B1-AD82-4EC5-8ABD-408E12CDFE42}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseDeCalcul" sheetId="2" state="hidden" r:id="rId1"/>
@@ -5713,6 +5713,12 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="19" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5731,12 +5737,6 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="22">
@@ -5764,20 +5764,6 @@
     <cellStyle name="TitreViolet" xfId="20" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
   </cellStyles>
   <dxfs count="32">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD0CECE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5813,6 +5799,20 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD0CECE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5871,20 +5871,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD0CECE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -5919,6 +5905,20 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD0CECE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -10951,85 +10951,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="82" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
+      <c r="A1" s="84" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
     </row>
     <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="84" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="82"/>
-      <c r="M2" s="82"/>
-      <c r="N2" s="82"/>
-      <c r="O2" s="82"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
     </row>
     <row r="3" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="85" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="84" t="s">
+      <c r="C3" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="84" t="s">
+      <c r="D3" s="86" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="84" t="s">
+      <c r="E3" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="84" t="s">
+      <c r="F3" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="84" t="s">
+      <c r="G3" s="86" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="84" t="s">
+      <c r="H3" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="84" t="s">
+      <c r="I3" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="84" t="s">
+      <c r="J3" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="84" t="s">
+      <c r="K3" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="84" t="s">
+      <c r="L3" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="84" t="s">
+      <c r="M3" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="84" t="s">
+      <c r="N3" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="84" t="s">
+      <c r="O3" s="86" t="s">
         <v>33</v>
       </c>
       <c r="P3" s="17"/>
@@ -11038,40 +11038,40 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="18"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="84"/>
-      <c r="M4" s="84"/>
-      <c r="N4" s="84"/>
-      <c r="O4" s="84"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="86"/>
+      <c r="K4" s="86"/>
+      <c r="L4" s="86"/>
+      <c r="M4" s="86"/>
+      <c r="N4" s="86"/>
+      <c r="O4" s="86"/>
       <c r="P4" s="17"/>
       <c r="Q4" s="17"/>
       <c r="R4" s="17"/>
     </row>
     <row r="5" spans="1:18" ht="59.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="18"/>
-      <c r="B5" s="83"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
-      <c r="L5" s="84"/>
-      <c r="M5" s="84"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="86"/>
+      <c r="D5" s="86"/>
+      <c r="E5" s="86"/>
+      <c r="F5" s="86"/>
+      <c r="G5" s="86"/>
+      <c r="H5" s="86"/>
+      <c r="I5" s="86"/>
+      <c r="J5" s="86"/>
+      <c r="K5" s="86"/>
+      <c r="L5" s="86"/>
+      <c r="M5" s="86"/>
+      <c r="N5" s="86"/>
+      <c r="O5" s="86"/>
       <c r="P5" s="17"/>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
@@ -11700,32 +11700,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="87" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
+      <c r="A1" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="88" t="s">
+      <c r="A3" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="85"/>
-      <c r="C4" s="86"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="88"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="59"/>
@@ -11817,10 +11817,10 @@
       <c r="G1" s="63" t="s">
         <v>102</v>
       </c>
-      <c r="H1" s="89" t="s">
+      <c r="H1" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="I1" s="90" t="s">
+      <c r="I1" s="83" t="s">
         <v>164</v>
       </c>
       <c r="J1" s="46" t="s">
@@ -11854,12 +11854,12 @@
       <c r="H2" s="79"/>
       <c r="I2" s="71"/>
       <c r="J2" s="61" t="str">
-        <f>IF(AND(E2="NC",G2=""),"Il manque un message d'erreur",
+        <f t="shared" ref="J2:J24" si="0">IF(AND(E2="NC",G2=""),"Il manque un message d'erreur",
    IF(AND(E2&lt;&gt;"NC",G2&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
         <v/>
       </c>
       <c r="K2" s="43">
-        <f>E2</f>
+        <f t="shared" ref="K2:K33" si="1">E2</f>
         <v>0</v>
       </c>
       <c r="L2" s="48">
@@ -11888,12 +11888,11 @@
       <c r="H3" s="79"/>
       <c r="I3" s="71"/>
       <c r="J3" s="61" t="str">
-        <f>IF(AND(E3="NC",G3=""),"Il manque un message d'erreur",
-   IF(AND(E3&lt;&gt;"NC",G3&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K3" s="43">
-        <f>E3</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L3" s="48">
@@ -11925,12 +11924,11 @@
       <c r="H4" s="79"/>
       <c r="I4" s="71"/>
       <c r="J4" s="61" t="str">
-        <f>IF(AND(E4="NC",G4=""),"Il manque un message d'erreur",
-   IF(AND(E4&lt;&gt;"NC",G4&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K4" s="43">
-        <f>E4</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L4" s="48">
@@ -11959,12 +11957,11 @@
       <c r="H5" s="79"/>
       <c r="I5" s="80"/>
       <c r="J5" s="61" t="str">
-        <f>IF(AND(E5="NC",G5=""),"Il manque un message d'erreur",
-   IF(AND(E5&lt;&gt;"NC",G5&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K5" s="43">
-        <f>E5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L5" s="48">
@@ -11993,12 +11990,11 @@
       <c r="H6" s="79"/>
       <c r="I6" s="80"/>
       <c r="J6" s="61" t="str">
-        <f>IF(AND(E6="NC",G6=""),"Il manque un message d'erreur",
-   IF(AND(E6&lt;&gt;"NC",G6&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K6" s="43">
-        <f>E6</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L6" s="48">
@@ -12030,12 +12026,11 @@
       <c r="H7" s="79"/>
       <c r="I7" s="80"/>
       <c r="J7" s="61" t="str">
-        <f>IF(AND(E7="NC",G7=""),"Il manque un message d'erreur",
-   IF(AND(E7&lt;&gt;"NC",G7&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K7" s="43">
-        <f>E7</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L7" s="48">
@@ -12067,12 +12062,11 @@
       <c r="H8" s="79"/>
       <c r="I8" s="71"/>
       <c r="J8" s="61" t="str">
-        <f>IF(AND(E8="NC",G8=""),"Il manque un message d'erreur",
-   IF(AND(E8&lt;&gt;"NC",G8&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K8" s="43">
-        <f>E8</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L8" s="48">
@@ -12101,12 +12095,11 @@
       <c r="H9" s="79"/>
       <c r="I9" s="71"/>
       <c r="J9" s="61" t="str">
-        <f>IF(AND(E9="NC",G9=""),"Il manque un message d'erreur",
-   IF(AND(E9&lt;&gt;"NC",G9&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K9" s="43">
-        <f>E9</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L9" s="48">
@@ -12135,12 +12128,11 @@
       <c r="H10" s="79"/>
       <c r="I10" s="80"/>
       <c r="J10" s="61" t="str">
-        <f>IF(AND(E10="NC",G10=""),"Il manque un message d'erreur",
-   IF(AND(E10&lt;&gt;"NC",G10&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K10" s="43">
-        <f>E10</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L10" s="48">
@@ -12169,12 +12161,11 @@
       <c r="H11" s="79"/>
       <c r="I11" s="80"/>
       <c r="J11" s="61" t="str">
-        <f>IF(AND(E11="NC",G11=""),"Il manque un message d'erreur",
-   IF(AND(E11&lt;&gt;"NC",G11&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K11" s="43">
-        <f>E11</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L11" s="48">
@@ -12203,12 +12194,11 @@
       <c r="H12" s="79"/>
       <c r="I12" s="71"/>
       <c r="J12" s="61" t="str">
-        <f>IF(AND(E12="NC",G12=""),"Il manque un message d'erreur",
-   IF(AND(E12&lt;&gt;"NC",G12&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K12" s="43">
-        <f>E12</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L12" s="48">
@@ -12240,12 +12230,11 @@
       <c r="H13" s="79"/>
       <c r="I13" s="71"/>
       <c r="J13" s="61" t="str">
-        <f>IF(AND(E13="NC",G13=""),"Il manque un message d'erreur",
-   IF(AND(E13&lt;&gt;"NC",G13&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K13" s="43">
-        <f>E13</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L13" s="48">
@@ -12277,12 +12266,11 @@
       <c r="H14" s="79"/>
       <c r="I14" s="71"/>
       <c r="J14" s="61" t="str">
-        <f>IF(AND(E14="NC",G14=""),"Il manque un message d'erreur",
-   IF(AND(E14&lt;&gt;"NC",G14&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K14" s="43">
-        <f>E14</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="48">
@@ -12314,12 +12302,11 @@
       <c r="H15" s="79"/>
       <c r="I15" s="71"/>
       <c r="J15" s="61" t="str">
-        <f>IF(AND(E15="NC",G15=""),"Il manque un message d'erreur",
-   IF(AND(E15&lt;&gt;"NC",G15&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K15" s="43">
-        <f>E15</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L15" s="48">
@@ -12348,12 +12335,11 @@
       <c r="H16" s="79"/>
       <c r="I16" s="71"/>
       <c r="J16" s="61" t="str">
-        <f>IF(AND(E16="NC",G16=""),"Il manque un message d'erreur",
-   IF(AND(E16&lt;&gt;"NC",G16&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K16" s="43">
-        <f>E16</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L16" s="48">
@@ -12385,12 +12371,11 @@
       <c r="H17" s="79"/>
       <c r="I17" s="71"/>
       <c r="J17" s="61" t="str">
-        <f>IF(AND(E17="NC",G17=""),"Il manque un message d'erreur",
-   IF(AND(E17&lt;&gt;"NC",G17&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K17" s="43">
-        <f>E17</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L17" s="48">
@@ -12419,12 +12404,11 @@
       <c r="H18" s="79"/>
       <c r="I18" s="71"/>
       <c r="J18" s="61" t="str">
-        <f>IF(AND(E18="NC",G18=""),"Il manque un message d'erreur",
-   IF(AND(E18&lt;&gt;"NC",G18&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K18" s="43">
-        <f>E18</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L18" s="48">
@@ -12456,12 +12440,11 @@
       <c r="H19" s="79"/>
       <c r="I19" s="71"/>
       <c r="J19" s="61" t="str">
-        <f>IF(AND(E19="NC",G19=""),"Il manque un message d'erreur",
-   IF(AND(E19&lt;&gt;"NC",G19&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K19" s="43">
-        <f>E19</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L19" s="48">
@@ -12490,12 +12473,11 @@
       <c r="H20" s="79"/>
       <c r="I20" s="80"/>
       <c r="J20" s="61" t="str">
-        <f>IF(AND(E20="NC",G20=""),"Il manque un message d'erreur",
-   IF(AND(E20&lt;&gt;"NC",G20&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K20" s="43">
-        <f>E20</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L20" s="48">
@@ -12527,12 +12509,11 @@
       <c r="H21" s="79"/>
       <c r="I21" s="71"/>
       <c r="J21" s="61" t="str">
-        <f>IF(AND(E21="NC",G21=""),"Il manque un message d'erreur",
-   IF(AND(E21&lt;&gt;"NC",G21&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K21" s="43">
-        <f>E21</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L21" s="48">
@@ -12561,12 +12542,11 @@
       <c r="H22" s="79"/>
       <c r="I22" s="80"/>
       <c r="J22" s="61" t="str">
-        <f>IF(AND(E22="NC",G22=""),"Il manque un message d'erreur",
-   IF(AND(E22&lt;&gt;"NC",G22&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K22" s="43">
-        <f>E22</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L22" s="48">
@@ -12595,12 +12575,11 @@
       <c r="H23" s="79"/>
       <c r="I23" s="80"/>
       <c r="J23" s="61" t="str">
-        <f>IF(AND(E23="NC",G23=""),"Il manque un message d'erreur",
-   IF(AND(E23&lt;&gt;"NC",G23&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K23" s="43">
-        <f>E23</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L23" s="48">
@@ -12629,12 +12608,11 @@
       <c r="H24" s="79"/>
       <c r="I24" s="80"/>
       <c r="J24" s="61" t="str">
-        <f>IF(AND(E24="NC",G24=""),"Il manque un message d'erreur",
-   IF(AND(E24&lt;&gt;"NC",G24&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K24" s="43">
-        <f>E24</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L24" s="48">
@@ -12664,7 +12642,7 @@
       <c r="I25" s="80"/>
       <c r="J25" s="61"/>
       <c r="K25" s="43">
-        <f>E25</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L25" s="48">
@@ -12693,12 +12671,12 @@
       <c r="H26" s="79"/>
       <c r="I26" s="71"/>
       <c r="J26" s="61" t="str">
-        <f>IF(AND(E26="NC",G26=""),"Il manque un message d'erreur",
+        <f t="shared" ref="J26:J54" si="2">IF(AND(E26="NC",G26=""),"Il manque un message d'erreur",
    IF(AND(E26&lt;&gt;"NC",G26&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
         <v/>
       </c>
       <c r="K26" s="43">
-        <f>E26</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L26" s="48">
@@ -12727,12 +12705,11 @@
       <c r="H27" s="79"/>
       <c r="I27" s="71"/>
       <c r="J27" s="61" t="str">
-        <f>IF(AND(E27="NC",G27=""),"Il manque un message d'erreur",
-   IF(AND(E27&lt;&gt;"NC",G27&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K27" s="43">
-        <f>E27</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L27" s="48">
@@ -12764,12 +12741,11 @@
       <c r="H28" s="79"/>
       <c r="I28" s="71"/>
       <c r="J28" s="61" t="str">
-        <f>IF(AND(E28="NC",G28=""),"Il manque un message d'erreur",
-   IF(AND(E28&lt;&gt;"NC",G28&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K28" s="43">
-        <f>E28</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L28" s="48">
@@ -12798,12 +12774,11 @@
       <c r="H29" s="79"/>
       <c r="I29" s="71"/>
       <c r="J29" s="61" t="str">
-        <f>IF(AND(E29="NC",G29=""),"Il manque un message d'erreur",
-   IF(AND(E29&lt;&gt;"NC",G29&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K29" s="43">
-        <f>E29</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L29" s="48">
@@ -12832,12 +12807,11 @@
       <c r="H30" s="79"/>
       <c r="I30" s="71"/>
       <c r="J30" s="61" t="str">
-        <f>IF(AND(E30="NC",G30=""),"Il manque un message d'erreur",
-   IF(AND(E30&lt;&gt;"NC",G30&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K30" s="43">
-        <f>E30</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L30" s="48">
@@ -12866,12 +12840,11 @@
       <c r="H31" s="79"/>
       <c r="I31" s="71"/>
       <c r="J31" s="61" t="str">
-        <f>IF(AND(E31="NC",G31=""),"Il manque un message d'erreur",
-   IF(AND(E31&lt;&gt;"NC",G31&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K31" s="43">
-        <f>E31</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L31" s="48">
@@ -12903,12 +12876,11 @@
       <c r="H32" s="79"/>
       <c r="I32" s="71"/>
       <c r="J32" s="61" t="str">
-        <f>IF(AND(E32="NC",G32=""),"Il manque un message d'erreur",
-   IF(AND(E32&lt;&gt;"NC",G32&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K32" s="43">
-        <f>E32</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L32" s="48">
@@ -12937,12 +12909,11 @@
       <c r="H33" s="79"/>
       <c r="I33" s="71"/>
       <c r="J33" s="61" t="str">
-        <f>IF(AND(E33="NC",G33=""),"Il manque un message d'erreur",
-   IF(AND(E33&lt;&gt;"NC",G33&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K33" s="43">
-        <f>E33</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L33" s="48">
@@ -12971,12 +12942,11 @@
       <c r="H34" s="79"/>
       <c r="I34" s="80"/>
       <c r="J34" s="61" t="str">
-        <f>IF(AND(E34="NC",G34=""),"Il manque un message d'erreur",
-   IF(AND(E34&lt;&gt;"NC",G34&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K34" s="43">
-        <f>E34</f>
+        <f t="shared" ref="K34:K54" si="3">E34</f>
         <v>0</v>
       </c>
       <c r="L34" s="48">
@@ -13005,12 +12975,11 @@
       <c r="H35" s="79"/>
       <c r="I35" s="80"/>
       <c r="J35" s="61" t="str">
-        <f>IF(AND(E35="NC",G35=""),"Il manque un message d'erreur",
-   IF(AND(E35&lt;&gt;"NC",G35&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K35" s="43">
-        <f>E35</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L35" s="48">
@@ -13039,12 +13008,11 @@
       <c r="H36" s="79"/>
       <c r="I36" s="80"/>
       <c r="J36" s="61" t="str">
-        <f>IF(AND(E36="NC",G36=""),"Il manque un message d'erreur",
-   IF(AND(E36&lt;&gt;"NC",G36&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K36" s="43">
-        <f>E36</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L36" s="48">
@@ -13073,12 +13041,11 @@
       <c r="H37" s="79"/>
       <c r="I37" s="80"/>
       <c r="J37" s="61" t="str">
-        <f>IF(AND(E37="NC",G37=""),"Il manque un message d'erreur",
-   IF(AND(E37&lt;&gt;"NC",G37&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K37" s="43">
-        <f>E37</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L37" s="48">
@@ -13107,12 +13074,11 @@
       <c r="H38" s="79"/>
       <c r="I38" s="81"/>
       <c r="J38" s="61" t="str">
-        <f>IF(AND(E38="NC",G38=""),"Il manque un message d'erreur",
-   IF(AND(E38&lt;&gt;"NC",G38&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K38" s="43">
-        <f>E38</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L38" s="48">
@@ -13141,12 +13107,11 @@
       <c r="H39" s="79"/>
       <c r="I39" s="71"/>
       <c r="J39" s="61" t="str">
-        <f>IF(AND(E39="NC",G39=""),"Il manque un message d'erreur",
-   IF(AND(E39&lt;&gt;"NC",G39&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K39" s="43">
-        <f>E39</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L39" s="48">
@@ -13175,12 +13140,11 @@
       <c r="H40" s="79"/>
       <c r="I40" s="80"/>
       <c r="J40" s="61" t="str">
-        <f>IF(AND(E40="NC",G40=""),"Il manque un message d'erreur",
-   IF(AND(E40&lt;&gt;"NC",G40&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K40" s="43">
-        <f>E40</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L40" s="48">
@@ -13209,12 +13173,11 @@
       <c r="H41" s="79"/>
       <c r="I41" s="71"/>
       <c r="J41" s="61" t="str">
-        <f>IF(AND(E41="NC",G41=""),"Il manque un message d'erreur",
-   IF(AND(E41&lt;&gt;"NC",G41&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K41" s="43">
-        <f>E41</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L41" s="48">
@@ -13243,12 +13206,11 @@
       <c r="H42" s="79"/>
       <c r="I42" s="71"/>
       <c r="J42" s="61" t="str">
-        <f>IF(AND(E42="NC",G42=""),"Il manque un message d'erreur",
-   IF(AND(E42&lt;&gt;"NC",G42&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K42" s="43">
-        <f>E42</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L42" s="48">
@@ -13280,12 +13242,11 @@
       <c r="H43" s="79"/>
       <c r="I43" s="71"/>
       <c r="J43" s="61" t="str">
-        <f>IF(AND(E43="NC",G43=""),"Il manque un message d'erreur",
-   IF(AND(E43&lt;&gt;"NC",G43&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K43" s="43">
-        <f>E43</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L43" s="48">
@@ -13317,12 +13278,11 @@
       <c r="H44" s="79"/>
       <c r="I44" s="71"/>
       <c r="J44" s="61" t="str">
-        <f>IF(AND(E44="NC",G44=""),"Il manque un message d'erreur",
-   IF(AND(E44&lt;&gt;"NC",G44&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K44" s="43">
-        <f>E44</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L44" s="48">
@@ -13351,12 +13311,11 @@
       <c r="H45" s="79"/>
       <c r="I45" s="71"/>
       <c r="J45" s="61" t="str">
-        <f>IF(AND(E45="NC",G45=""),"Il manque un message d'erreur",
-   IF(AND(E45&lt;&gt;"NC",G45&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K45" s="43">
-        <f>E45</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L45" s="48">
@@ -13385,12 +13344,11 @@
       <c r="H46" s="79"/>
       <c r="I46" s="71"/>
       <c r="J46" s="61" t="str">
-        <f>IF(AND(E46="NC",G46=""),"Il manque un message d'erreur",
-   IF(AND(E46&lt;&gt;"NC",G46&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K46" s="43">
-        <f>E46</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L46" s="48">
@@ -13419,12 +13377,11 @@
       <c r="H47" s="79"/>
       <c r="I47" s="71"/>
       <c r="J47" s="61" t="str">
-        <f>IF(AND(E47="NC",G47=""),"Il manque un message d'erreur",
-   IF(AND(E47&lt;&gt;"NC",G47&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K47" s="43">
-        <f>E47</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L47" s="48">
@@ -13453,12 +13410,11 @@
       <c r="H48" s="79"/>
       <c r="I48" s="80"/>
       <c r="J48" s="61" t="str">
-        <f>IF(AND(E48="NC",G48=""),"Il manque un message d'erreur",
-   IF(AND(E48&lt;&gt;"NC",G48&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K48" s="43">
-        <f>E48</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L48" s="48">
@@ -13487,12 +13443,11 @@
       <c r="H49" s="79"/>
       <c r="I49" s="80"/>
       <c r="J49" s="61" t="str">
-        <f>IF(AND(E49="NC",G49=""),"Il manque un message d'erreur",
-   IF(AND(E49&lt;&gt;"NC",G49&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K49" s="43">
-        <f>E49</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L49" s="48">
@@ -13521,12 +13476,11 @@
       <c r="H50" s="79"/>
       <c r="I50" s="80"/>
       <c r="J50" s="61" t="str">
-        <f>IF(AND(E50="NC",G50=""),"Il manque un message d'erreur",
-   IF(AND(E50&lt;&gt;"NC",G50&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K50" s="43">
-        <f>E50</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L50" s="48">
@@ -13555,12 +13509,11 @@
       <c r="H51" s="79"/>
       <c r="I51" s="71"/>
       <c r="J51" s="61" t="str">
-        <f>IF(AND(E51="NC",G51=""),"Il manque un message d'erreur",
-   IF(AND(E51&lt;&gt;"NC",G51&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K51" s="43">
-        <f>E51</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L51" s="48">
@@ -13589,12 +13542,11 @@
       <c r="H52" s="79"/>
       <c r="I52" s="71"/>
       <c r="J52" s="61" t="str">
-        <f>IF(AND(E52="NC",G52=""),"Il manque un message d'erreur",
-   IF(AND(E52&lt;&gt;"NC",G52&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K52" s="43">
-        <f>E52</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L52" s="48">
@@ -13623,12 +13575,11 @@
       <c r="H53" s="79"/>
       <c r="I53" s="71"/>
       <c r="J53" s="61" t="str">
-        <f>IF(AND(E53="NC",G53=""),"Il manque un message d'erreur",
-   IF(AND(E53&lt;&gt;"NC",G53&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K53" s="43">
-        <f>E53</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L53" s="48">
@@ -13657,12 +13608,11 @@
       <c r="H54" s="79"/>
       <c r="I54" s="71"/>
       <c r="J54" s="61" t="str">
-        <f>IF(AND(E54="NC",G54=""),"Il manque un message d'erreur",
-   IF(AND(E54&lt;&gt;"NC",G54&lt;&gt;""),"Il faut seulement écrire un message d'erreur pour NC",""))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K54" s="43">
-        <f>E54</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L54" s="48">
@@ -13688,7 +13638,7 @@
       <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D48 E1 H1 E55:E1048576 H55:H1048576">
+  <conditionalFormatting sqref="E1 H1 D48 E55:E1048576 H55:H1048576">
     <cfRule type="cellIs" dxfId="29" priority="13" operator="equal">
       <formula>"NT"</formula>
     </cfRule>
@@ -13767,10 +13717,10 @@
       <c r="G1" s="63" t="s">
         <v>102</v>
       </c>
-      <c r="H1" s="89" t="s">
+      <c r="H1" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="I1" s="90" t="s">
+      <c r="I1" s="83" t="s">
         <v>164</v>
       </c>
       <c r="J1" s="78" t="s">
@@ -15604,11 +15554,21 @@
       <formula>"NT"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H1 H55:H1048576">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
+      <formula>"NT"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H54">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+      <formula>"NT"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="duplicateValues" dxfId="17" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J54">
-    <cfRule type="notContainsBlanks" dxfId="16" priority="72">
+    <cfRule type="notContainsBlanks" dxfId="14" priority="72">
       <formula>LEN(TRIM(J2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15618,21 +15578,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:M1">
-    <cfRule type="duplicateValues" dxfId="15" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:M1048576">
-    <cfRule type="cellIs" dxfId="14" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="9" operator="equal">
       <formula>"NC"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1 H55:H1048576">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
-      <formula>"NT"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H54">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
-      <formula>"NT"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15683,10 +15633,10 @@
       <c r="G1" s="63" t="s">
         <v>102</v>
       </c>
-      <c r="H1" s="89" t="s">
+      <c r="H1" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="I1" s="90" t="s">
+      <c r="I1" s="83" t="s">
         <v>164</v>
       </c>
       <c r="J1" s="78" t="s">
@@ -17520,11 +17470,21 @@
       <formula>"NT"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H1 H55:H1048576">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+      <formula>"NT"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H54">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"NT"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J54">
-    <cfRule type="notContainsBlanks" dxfId="4" priority="75">
+    <cfRule type="notContainsBlanks" dxfId="2" priority="75">
       <formula>LEN(TRIM(J2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17534,21 +17494,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:M1">
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:M1048576">
-    <cfRule type="cellIs" dxfId="2" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
       <formula>"NC"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1 H55:H1048576">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"NT"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H54">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"NT"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
